--- a/research/traditional_assets/database/data/peru/peru_green_renewable_energy.xlsx
+++ b/research/traditional_assets/database/data/peru/peru_green_renewable_energy.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.08316605570672644</v>
+        <v>0.0829524408423916</v>
       </c>
       <c r="C2">
-        <v>2007.873491396034</v>
+        <v>1991.250726564692</v>
       </c>
       <c r="D2">
-        <v>1909.373491396034</v>
+        <v>1912.831426564692</v>
       </c>
       <c r="E2">
-        <v>-4.97</v>
+        <v>15.1107</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>20.0807</v>
       </c>
       <c r="G2">
         <v>98.5</v>
@@ -1451,28 +1451,28 @@
         <v>401.1</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>1.01005921</v>
       </c>
       <c r="N2">
-        <v>401.1</v>
+        <v>400.08994079</v>
       </c>
       <c r="O2">
-        <v>118.3245</v>
+        <v>118.02653253305</v>
       </c>
       <c r="P2">
-        <v>282.7755</v>
+        <v>282.06340825695</v>
       </c>
       <c r="Q2">
-        <v>285.1755</v>
+        <v>284.46340825695</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.08316605570672644</v>
+        <v>0.08343214731554707</v>
       </c>
       <c r="T2">
-        <v>0.5780409979533054</v>
+        <v>0.582157350514488</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>397.1054330567413</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.0829524408423916</v>
+        <v>0.08273882597805675</v>
       </c>
       <c r="C3">
-        <v>1991.250726564692</v>
+        <v>1974.640509315106</v>
       </c>
       <c r="D3">
-        <v>1912.831426564692</v>
+        <v>1916.301909315106</v>
       </c>
       <c r="E3">
-        <v>15.1107</v>
+        <v>35.1914</v>
       </c>
       <c r="F3">
-        <v>20.0807</v>
+        <v>40.1614</v>
       </c>
       <c r="G3">
         <v>98.5</v>
@@ -1533,28 +1533,28 @@
         <v>401.1</v>
       </c>
       <c r="M3">
-        <v>1.01005921</v>
+        <v>2.02011842</v>
       </c>
       <c r="N3">
-        <v>400.08994079</v>
+        <v>399.07988158</v>
       </c>
       <c r="O3">
-        <v>118.02653253305</v>
+        <v>117.7285650661</v>
       </c>
       <c r="P3">
-        <v>282.06340825695</v>
+        <v>281.3513165139</v>
       </c>
       <c r="Q3">
-        <v>284.46340825695</v>
+        <v>283.7513165139</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.08343214731554707</v>
+        <v>0.08370366936536403</v>
       </c>
       <c r="T3">
-        <v>0.582157350514488</v>
+        <v>0.5863577102707969</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>397.1054330567413</v>
+        <v>198.5527165283707</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.08273882597805675</v>
+        <v>0.08252521111372189</v>
       </c>
       <c r="C4">
-        <v>1974.640509315106</v>
+        <v>1958.042908067286</v>
       </c>
       <c r="D4">
-        <v>1916.301909315106</v>
+        <v>1919.785008067286</v>
       </c>
       <c r="E4">
-        <v>35.1914</v>
+        <v>55.27209999999999</v>
       </c>
       <c r="F4">
-        <v>40.1614</v>
+        <v>60.24209999999999</v>
       </c>
       <c r="G4">
         <v>98.5</v>
@@ -1615,28 +1615,28 @@
         <v>401.1</v>
       </c>
       <c r="M4">
-        <v>2.02011842</v>
+        <v>3.030177629999999</v>
       </c>
       <c r="N4">
-        <v>399.07988158</v>
+        <v>398.06982237</v>
       </c>
       <c r="O4">
-        <v>117.7285650661</v>
+        <v>117.43059759915</v>
       </c>
       <c r="P4">
-        <v>281.3513165139</v>
+        <v>280.63922477085</v>
       </c>
       <c r="Q4">
-        <v>283.7513165139</v>
+        <v>283.03922477085</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08370366936536403</v>
+        <v>0.08398078980796073</v>
       </c>
       <c r="T4">
-        <v>0.5863577102707969</v>
+        <v>0.5906446753829059</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>198.5527165283707</v>
+        <v>132.3684776855804</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.08252521111372189</v>
+        <v>0.08231159624938705</v>
       </c>
       <c r="C5">
-        <v>1958.042908067286</v>
+        <v>1941.457991739597</v>
       </c>
       <c r="D5">
-        <v>1919.785008067286</v>
+        <v>1923.280791739597</v>
       </c>
       <c r="E5">
-        <v>55.27209999999999</v>
+        <v>75.3528</v>
       </c>
       <c r="F5">
-        <v>60.24209999999999</v>
+        <v>80.3228</v>
       </c>
       <c r="G5">
         <v>98.5</v>
@@ -1697,28 +1697,28 @@
         <v>401.1</v>
       </c>
       <c r="M5">
-        <v>3.030177629999999</v>
+        <v>4.040236839999999</v>
       </c>
       <c r="N5">
-        <v>398.06982237</v>
+        <v>397.05976316</v>
       </c>
       <c r="O5">
-        <v>117.43059759915</v>
+        <v>117.1326301322</v>
       </c>
       <c r="P5">
-        <v>280.63922477085</v>
+        <v>279.9271330278</v>
       </c>
       <c r="Q5">
-        <v>283.03922477085</v>
+        <v>282.3271330278</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.08398078980796073</v>
+        <v>0.08426368359311152</v>
       </c>
       <c r="T5">
-        <v>0.5906446753829059</v>
+        <v>0.5950209522681837</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>132.3684776855804</v>
+        <v>99.27635826418535</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.08231159624938705</v>
+        <v>0.08209798138505223</v>
       </c>
       <c r="C6">
-        <v>1941.457991739597</v>
+        <v>1924.885829753296</v>
       </c>
       <c r="D6">
-        <v>1923.280791739597</v>
+        <v>1926.789329753296</v>
       </c>
       <c r="E6">
-        <v>75.3528</v>
+        <v>95.43350000000001</v>
       </c>
       <c r="F6">
-        <v>80.3228</v>
+        <v>100.4035</v>
       </c>
       <c r="G6">
         <v>98.5</v>
@@ -1779,28 +1779,28 @@
         <v>401.1</v>
       </c>
       <c r="M6">
-        <v>4.040236839999999</v>
+        <v>5.05029605</v>
       </c>
       <c r="N6">
-        <v>397.05976316</v>
+        <v>396.04970395</v>
       </c>
       <c r="O6">
-        <v>117.1326301322</v>
+        <v>116.83466266525</v>
       </c>
       <c r="P6">
-        <v>279.9271330278</v>
+        <v>279.21504128475</v>
       </c>
       <c r="Q6">
-        <v>282.3271330278</v>
+        <v>281.61504128475</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.08426368359311152</v>
+        <v>0.08455253303689708</v>
       </c>
       <c r="T6">
-        <v>0.5950209522681837</v>
+        <v>0.5994893612984149</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>99.27635826418535</v>
+        <v>79.42108661134827</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.08209798138505223</v>
+        <v>0.08188436652071737</v>
       </c>
       <c r="C7">
-        <v>1924.885829753296</v>
+        <v>1908.326492037135</v>
       </c>
       <c r="D7">
-        <v>1926.789329753296</v>
+        <v>1930.310692037135</v>
       </c>
       <c r="E7">
-        <v>95.43350000000001</v>
+        <v>115.5142</v>
       </c>
       <c r="F7">
-        <v>100.4035</v>
+        <v>120.4842</v>
       </c>
       <c r="G7">
         <v>98.5</v>
@@ -1861,28 +1861,28 @@
         <v>401.1</v>
       </c>
       <c r="M7">
-        <v>5.05029605</v>
+        <v>6.06035526</v>
       </c>
       <c r="N7">
-        <v>396.04970395</v>
+        <v>395.03964474</v>
       </c>
       <c r="O7">
-        <v>116.83466266525</v>
+        <v>116.5366951983</v>
       </c>
       <c r="P7">
-        <v>279.21504128475</v>
+        <v>278.5029495417</v>
       </c>
       <c r="Q7">
-        <v>281.61504128475</v>
+        <v>280.9029495417</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.08455253303689708</v>
+        <v>0.08484752821352912</v>
       </c>
       <c r="T7">
-        <v>0.5994893612984149</v>
+        <v>0.6040528428612041</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>79.42108661134827</v>
+        <v>66.18423884279022</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08188436652071737</v>
+        <v>0.08167075165638255</v>
       </c>
       <c r="C8">
-        <v>1908.326492037135</v>
+        <v>1891.780049032</v>
       </c>
       <c r="D8">
-        <v>1930.310692037135</v>
+        <v>1933.844949032</v>
       </c>
       <c r="E8">
-        <v>115.5142</v>
+        <v>135.5949</v>
       </c>
       <c r="F8">
-        <v>120.4842</v>
+        <v>140.5649</v>
       </c>
       <c r="G8">
         <v>98.5</v>
@@ -1943,28 +1943,28 @@
         <v>401.1</v>
       </c>
       <c r="M8">
-        <v>6.060355259999999</v>
+        <v>7.070414469999999</v>
       </c>
       <c r="N8">
-        <v>395.03964474</v>
+        <v>394.02958553</v>
       </c>
       <c r="O8">
-        <v>116.5366951983</v>
+        <v>116.23872773135</v>
       </c>
       <c r="P8">
-        <v>278.5029495417</v>
+        <v>277.79085779865</v>
       </c>
       <c r="Q8">
-        <v>280.9029495417</v>
+        <v>280.19085779865</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.08484752821352912</v>
+        <v>0.08514886737245433</v>
       </c>
       <c r="T8">
-        <v>0.6040528428612041</v>
+        <v>0.6087144638124404</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>66.18423884279024</v>
+        <v>56.72934757953448</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.08167075165638253</v>
+        <v>0.0814571367920477</v>
       </c>
       <c r="C9">
-        <v>1891.780049032</v>
+        <v>1875.246571695614</v>
       </c>
       <c r="D9">
-        <v>1933.844949032</v>
+        <v>1937.392171695614</v>
       </c>
       <c r="E9">
-        <v>135.5949</v>
+        <v>155.6756</v>
       </c>
       <c r="F9">
-        <v>140.5649</v>
+        <v>160.6456</v>
       </c>
       <c r="G9">
         <v>98.5</v>
@@ -2025,28 +2025,28 @@
         <v>401.1</v>
       </c>
       <c r="M9">
-        <v>7.070414470000001</v>
+        <v>8.080473679999999</v>
       </c>
       <c r="N9">
-        <v>394.02958553</v>
+        <v>393.01952632</v>
       </c>
       <c r="O9">
-        <v>116.23872773135</v>
+        <v>115.9407602644</v>
       </c>
       <c r="P9">
-        <v>277.79085779865</v>
+        <v>277.0787660556</v>
       </c>
       <c r="Q9">
-        <v>280.19085779865</v>
+        <v>279.4787660556</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.08514886737245433</v>
+        <v>0.08545675738266054</v>
       </c>
       <c r="T9">
-        <v>0.6087144638124404</v>
+        <v>0.6134774243495732</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>56.72934757953446</v>
+        <v>49.63817913209267</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.0814571367920477</v>
+        <v>0.08124352192771285</v>
       </c>
       <c r="C10">
-        <v>1875.246571695614</v>
+        <v>1858.726131507285</v>
       </c>
       <c r="D10">
-        <v>1937.392171695614</v>
+        <v>1940.952431507285</v>
       </c>
       <c r="E10">
-        <v>155.6756</v>
+        <v>175.7563</v>
       </c>
       <c r="F10">
-        <v>160.6456</v>
+        <v>180.7263</v>
       </c>
       <c r="G10">
         <v>98.5</v>
@@ -2107,28 +2107,28 @@
         <v>401.1</v>
       </c>
       <c r="M10">
-        <v>8.080473679999999</v>
+        <v>9.090532889999999</v>
       </c>
       <c r="N10">
-        <v>393.01952632</v>
+        <v>392.00946711</v>
       </c>
       <c r="O10">
-        <v>115.9407602644</v>
+        <v>115.64279279745</v>
       </c>
       <c r="P10">
-        <v>277.0787660556</v>
+        <v>276.36667431255</v>
       </c>
       <c r="Q10">
-        <v>279.4787660556</v>
+        <v>278.76667431255</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.08545675738266054</v>
+        <v>0.08577141420627786</v>
       </c>
       <c r="T10">
-        <v>0.6134774243495732</v>
+        <v>0.6183450653380717</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>49.63817913209267</v>
+        <v>44.12282589519349</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.08124352192771285</v>
+        <v>0.081029907063378</v>
       </c>
       <c r="C11">
-        <v>1858.726131507285</v>
+        <v>1842.218800472703</v>
       </c>
       <c r="D11">
-        <v>1940.952431507285</v>
+        <v>1944.525800472703</v>
       </c>
       <c r="E11">
-        <v>175.7563</v>
+        <v>195.837</v>
       </c>
       <c r="F11">
-        <v>180.7263</v>
+        <v>200.807</v>
       </c>
       <c r="G11">
         <v>98.5</v>
@@ -2189,28 +2189,28 @@
         <v>401.1</v>
       </c>
       <c r="M11">
-        <v>9.090532889999999</v>
+        <v>10.1005921</v>
       </c>
       <c r="N11">
-        <v>392.00946711</v>
+        <v>390.9994079000001</v>
       </c>
       <c r="O11">
-        <v>115.64279279745</v>
+        <v>115.3448253305</v>
       </c>
       <c r="P11">
-        <v>276.36667431255</v>
+        <v>275.6545825695</v>
       </c>
       <c r="Q11">
-        <v>278.76667431255</v>
+        <v>278.0545825695</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.08577141420627786</v>
+        <v>0.08609306340375333</v>
       </c>
       <c r="T11">
-        <v>0.6183450653380717</v>
+        <v>0.6233208761263144</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>44.12282589519349</v>
+        <v>39.71054330567414</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.081029907063378</v>
+        <v>0.08081629219904317</v>
       </c>
       <c r="C12">
-        <v>1842.218800472703</v>
+        <v>1825.724651128797</v>
       </c>
       <c r="D12">
-        <v>1944.525800472703</v>
+        <v>1948.112351128797</v>
       </c>
       <c r="E12">
-        <v>195.837</v>
+        <v>215.9177</v>
       </c>
       <c r="F12">
-        <v>200.807</v>
+        <v>220.8877</v>
       </c>
       <c r="G12">
         <v>98.5</v>
@@ -2271,28 +2271,28 @@
         <v>401.1</v>
       </c>
       <c r="M12">
-        <v>10.1005921</v>
+        <v>11.11065131</v>
       </c>
       <c r="N12">
-        <v>390.9994079000001</v>
+        <v>389.98934869</v>
       </c>
       <c r="O12">
-        <v>115.3448253305</v>
+        <v>115.04685786355</v>
       </c>
       <c r="P12">
-        <v>275.6545825695</v>
+        <v>274.94249082645</v>
       </c>
       <c r="Q12">
-        <v>278.0545825695</v>
+        <v>277.34249082645</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.08609306340375333</v>
+        <v>0.0864219406730822</v>
       </c>
       <c r="T12">
-        <v>0.6233208761263144</v>
+        <v>0.6284085028873266</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>39.71054330567414</v>
+        <v>36.10049391424921</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.08081629219904317</v>
+        <v>0.08060267733470831</v>
       </c>
       <c r="C13">
-        <v>1825.724651128797</v>
+        <v>1809.243756548646</v>
       </c>
       <c r="D13">
-        <v>1948.112351128797</v>
+        <v>1951.712156548646</v>
       </c>
       <c r="E13">
-        <v>215.9177</v>
+        <v>235.9984</v>
       </c>
       <c r="F13">
-        <v>220.8877</v>
+        <v>240.9684</v>
       </c>
       <c r="G13">
         <v>98.5</v>
@@ -2353,28 +2353,28 @@
         <v>401.1</v>
       </c>
       <c r="M13">
-        <v>11.11065131</v>
+        <v>12.12071052</v>
       </c>
       <c r="N13">
-        <v>389.98934869</v>
+        <v>388.97928948</v>
       </c>
       <c r="O13">
-        <v>115.04685786355</v>
+        <v>114.7488903966</v>
       </c>
       <c r="P13">
-        <v>274.94249082645</v>
+        <v>274.2303990834</v>
       </c>
       <c r="Q13">
-        <v>277.34249082645</v>
+        <v>276.6303990834</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.0864219406730822</v>
+        <v>0.08675829242580491</v>
       </c>
       <c r="T13">
-        <v>0.6284085028873266</v>
+        <v>0.633611757529271</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>36.10049391424921</v>
+        <v>33.09211942139512</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.08060267733470831</v>
+        <v>0.08038906247037349</v>
       </c>
       <c r="C14">
-        <v>1809.243756548646</v>
+        <v>1792.776190346436</v>
       </c>
       <c r="D14">
-        <v>1951.712156548646</v>
+        <v>1955.325290346436</v>
       </c>
       <c r="E14">
-        <v>235.9984</v>
+        <v>256.0791</v>
       </c>
       <c r="F14">
-        <v>240.9684</v>
+        <v>261.0491</v>
       </c>
       <c r="G14">
         <v>98.5</v>
@@ -2435,28 +2435,28 @@
         <v>401.1</v>
       </c>
       <c r="M14">
-        <v>12.12071052</v>
+        <v>13.13076973</v>
       </c>
       <c r="N14">
-        <v>388.97928948</v>
+        <v>387.96923027</v>
       </c>
       <c r="O14">
-        <v>114.7488903966</v>
+        <v>114.45092292965</v>
       </c>
       <c r="P14">
-        <v>274.2303990834</v>
+        <v>273.51830734035</v>
       </c>
       <c r="Q14">
-        <v>276.6303990834</v>
+        <v>275.91830734035</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.08675829242580491</v>
+        <v>0.08710237640272814</v>
       </c>
       <c r="T14">
-        <v>0.633611757529271</v>
+        <v>0.6389346272204555</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>33.09211942139512</v>
+        <v>30.54657177359549</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.08038906247037349</v>
+        <v>0.08017544760603863</v>
       </c>
       <c r="C15">
-        <v>1792.776190346436</v>
+        <v>1776.322026682483</v>
       </c>
       <c r="D15">
-        <v>1955.325290346436</v>
+        <v>1958.951826682483</v>
       </c>
       <c r="E15">
-        <v>256.0791</v>
+        <v>276.1598</v>
       </c>
       <c r="F15">
-        <v>261.0491</v>
+        <v>281.1298</v>
       </c>
       <c r="G15">
         <v>98.5</v>
@@ -2517,28 +2517,28 @@
         <v>401.1</v>
       </c>
       <c r="M15">
-        <v>13.13076973</v>
+        <v>14.14082894</v>
       </c>
       <c r="N15">
-        <v>387.96923027</v>
+        <v>386.95917106</v>
       </c>
       <c r="O15">
-        <v>114.45092292965</v>
+        <v>114.1529554627</v>
       </c>
       <c r="P15">
-        <v>273.51830734035</v>
+        <v>272.8062155973</v>
       </c>
       <c r="Q15">
-        <v>275.91830734035</v>
+        <v>275.2062155973</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.08710237640272814</v>
+        <v>0.08745446233260307</v>
       </c>
       <c r="T15">
-        <v>0.6389346272204555</v>
+        <v>0.6443812845788767</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>30.54657177359549</v>
+        <v>28.36467378976723</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.08017544760603863</v>
+        <v>0.07996183274170379</v>
       </c>
       <c r="C16">
-        <v>1776.322026682483</v>
+        <v>1759.881340268305</v>
       </c>
       <c r="D16">
-        <v>1958.951826682483</v>
+        <v>1962.591840268306</v>
       </c>
       <c r="E16">
-        <v>276.1598</v>
+        <v>296.2405</v>
       </c>
       <c r="F16">
-        <v>281.1298</v>
+        <v>301.2105</v>
       </c>
       <c r="G16">
         <v>98.5</v>
@@ -2599,28 +2599,28 @@
         <v>401.1</v>
       </c>
       <c r="M16">
-        <v>14.14082894</v>
+        <v>15.15088815</v>
       </c>
       <c r="N16">
-        <v>386.95917106</v>
+        <v>385.94911185</v>
       </c>
       <c r="O16">
-        <v>114.1529554627</v>
+        <v>113.85498799575</v>
       </c>
       <c r="P16">
-        <v>272.8062155973</v>
+        <v>272.09412385425</v>
       </c>
       <c r="Q16">
-        <v>275.2062155973</v>
+        <v>274.49412385425</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.08745446233260307</v>
+        <v>0.08781483263729858</v>
       </c>
       <c r="T16">
-        <v>0.6443812845788767</v>
+        <v>0.6499560985810255</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>28.36467378976723</v>
+        <v>26.47369553711609</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.07996183274170379</v>
+        <v>0.07974821787736895</v>
       </c>
       <c r="C17">
-        <v>1759.881340268306</v>
+        <v>1743.454206371753</v>
       </c>
       <c r="D17">
-        <v>1962.591840268306</v>
+        <v>1966.245406371753</v>
       </c>
       <c r="E17">
-        <v>296.2404999999999</v>
+        <v>316.3212</v>
       </c>
       <c r="F17">
-        <v>301.2105</v>
+        <v>321.2912</v>
       </c>
       <c r="G17">
         <v>98.5</v>
@@ -2681,28 +2681,28 @@
         <v>401.1</v>
       </c>
       <c r="M17">
-        <v>15.15088815</v>
+        <v>16.16094736</v>
       </c>
       <c r="N17">
-        <v>385.94911185</v>
+        <v>384.93905264</v>
       </c>
       <c r="O17">
-        <v>113.85498799575</v>
+        <v>113.5570205288</v>
       </c>
       <c r="P17">
-        <v>272.09412385425</v>
+        <v>271.3820321112</v>
       </c>
       <c r="Q17">
-        <v>274.49412385425</v>
+        <v>273.7820321112</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.08781483263729858</v>
+        <v>0.08818378318734399</v>
       </c>
       <c r="T17">
-        <v>0.6499560985810255</v>
+        <v>0.6556636462498922</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>26.47369553711609</v>
+        <v>24.81908956604633</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.07974821787736895</v>
+        <v>0.07953460301303411</v>
       </c>
       <c r="C18">
-        <v>1743.454206371753</v>
+        <v>1727.040700822197</v>
       </c>
       <c r="D18">
-        <v>1966.245406371753</v>
+        <v>1969.912600822197</v>
       </c>
       <c r="E18">
-        <v>316.3212</v>
+        <v>336.4019</v>
       </c>
       <c r="F18">
-        <v>321.2912</v>
+        <v>341.3719</v>
       </c>
       <c r="G18">
         <v>98.5</v>
@@ -2763,28 +2763,28 @@
         <v>401.1</v>
       </c>
       <c r="M18">
-        <v>16.16094736</v>
+        <v>17.17100657</v>
       </c>
       <c r="N18">
-        <v>384.93905264</v>
+        <v>383.92899343</v>
       </c>
       <c r="O18">
-        <v>113.5570205288</v>
+        <v>113.25905306185</v>
       </c>
       <c r="P18">
-        <v>271.3820321112</v>
+        <v>270.66994036815</v>
       </c>
       <c r="Q18">
-        <v>273.7820321112</v>
+        <v>273.06994036815</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.08818378318734399</v>
+        <v>0.08856162411208929</v>
       </c>
       <c r="T18">
-        <v>0.6556636462498922</v>
+        <v>0.6615087251878882</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>24.81908956604633</v>
+        <v>23.35914312098479</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.07953460301303411</v>
+        <v>0.07932098814869927</v>
       </c>
       <c r="C19">
-        <v>1727.040700822197</v>
+        <v>1710.640900015776</v>
       </c>
       <c r="D19">
-        <v>1969.912600822197</v>
+        <v>1973.593500015776</v>
       </c>
       <c r="E19">
-        <v>336.4019</v>
+        <v>356.4826</v>
       </c>
       <c r="F19">
-        <v>341.3719</v>
+        <v>361.4526</v>
       </c>
       <c r="G19">
         <v>98.5</v>
@@ -2845,28 +2845,28 @@
         <v>401.1</v>
       </c>
       <c r="M19">
-        <v>17.17100657</v>
+        <v>18.18106578</v>
       </c>
       <c r="N19">
-        <v>383.92899343</v>
+        <v>382.91893422</v>
       </c>
       <c r="O19">
-        <v>113.25905306185</v>
+        <v>112.9610855949</v>
       </c>
       <c r="P19">
-        <v>270.66994036815</v>
+        <v>269.9578486251</v>
       </c>
       <c r="Q19">
-        <v>273.06994036815</v>
+        <v>272.3578486251</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.08856162411208929</v>
+        <v>0.08894868066914545</v>
       </c>
       <c r="T19">
-        <v>0.6615087251878882</v>
+        <v>0.6674963670268109</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>23.35914312098479</v>
+        <v>22.06141294759674</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.07932098814869928</v>
+        <v>0.07910737328436443</v>
       </c>
       <c r="C20">
-        <v>1710.640900015775</v>
+        <v>1694.254880920696</v>
       </c>
       <c r="D20">
-        <v>1973.593500015775</v>
+        <v>1977.288180920697</v>
       </c>
       <c r="E20">
-        <v>356.4825999999999</v>
+        <v>376.5633</v>
       </c>
       <c r="F20">
-        <v>361.4526</v>
+        <v>381.5333</v>
       </c>
       <c r="G20">
         <v>98.5</v>
@@ -2927,28 +2927,28 @@
         <v>401.1</v>
       </c>
       <c r="M20">
-        <v>18.18106578</v>
+        <v>19.19112499</v>
       </c>
       <c r="N20">
-        <v>382.91893422</v>
+        <v>381.90887501</v>
       </c>
       <c r="O20">
-        <v>112.9610855949</v>
+        <v>112.66311812795</v>
       </c>
       <c r="P20">
-        <v>269.9578486251</v>
+        <v>269.24575688205</v>
       </c>
       <c r="Q20">
-        <v>272.3578486251</v>
+        <v>271.64575688205</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.08894868066914545</v>
+        <v>0.08934529417822767</v>
       </c>
       <c r="T20">
-        <v>0.6674963670268109</v>
+        <v>0.673631851874102</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>22.06141294759674</v>
+        <v>20.90028595035481</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.07910737328436443</v>
+        <v>0.07889375842002959</v>
       </c>
       <c r="C21">
-        <v>1694.254880920696</v>
+        <v>1677.882721082608</v>
       </c>
       <c r="D21">
-        <v>1977.288180920697</v>
+        <v>1980.996721082608</v>
       </c>
       <c r="E21">
-        <v>376.5633</v>
+        <v>396.644</v>
       </c>
       <c r="F21">
-        <v>381.5333</v>
+        <v>401.614</v>
       </c>
       <c r="G21">
         <v>98.5</v>
@@ -3009,28 +3009,28 @@
         <v>401.1</v>
       </c>
       <c r="M21">
-        <v>19.19112499</v>
+        <v>20.2011842</v>
       </c>
       <c r="N21">
-        <v>381.90887501</v>
+        <v>380.8988158</v>
       </c>
       <c r="O21">
-        <v>112.66311812795</v>
+        <v>112.365150661</v>
       </c>
       <c r="P21">
-        <v>269.24575688205</v>
+        <v>268.533665139</v>
       </c>
       <c r="Q21">
-        <v>271.64575688205</v>
+        <v>270.933665139</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.08934529417822767</v>
+        <v>0.08975182302503698</v>
       </c>
       <c r="T21">
-        <v>0.673631851874102</v>
+        <v>0.6799207238425755</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>20.90028595035481</v>
+        <v>19.85527165283706</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.07889375842002959</v>
+        <v>0.07868014355569475</v>
       </c>
       <c r="C22">
-        <v>1677.882721082608</v>
+        <v>1661.524498630019</v>
       </c>
       <c r="D22">
-        <v>1980.996721082608</v>
+        <v>1984.719198630019</v>
       </c>
       <c r="E22">
-        <v>396.644</v>
+        <v>416.7247</v>
       </c>
       <c r="F22">
-        <v>401.614</v>
+        <v>421.6947</v>
       </c>
       <c r="G22">
         <v>98.5</v>
@@ -3091,28 +3091,28 @@
         <v>401.1</v>
       </c>
       <c r="M22">
-        <v>20.2011842</v>
+        <v>21.21124341</v>
       </c>
       <c r="N22">
-        <v>380.8988158</v>
+        <v>379.88875659</v>
       </c>
       <c r="O22">
-        <v>112.365150661</v>
+        <v>112.06718319405</v>
       </c>
       <c r="P22">
-        <v>268.533665139</v>
+        <v>267.82157339595</v>
       </c>
       <c r="Q22">
-        <v>270.933665139</v>
+        <v>270.22157339595</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.08975182302503698</v>
+        <v>0.09016864374138575</v>
       </c>
       <c r="T22">
-        <v>0.6799207238425755</v>
+        <v>0.6863688077596179</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>19.85527165283706</v>
+        <v>18.90978252651149</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.07868014355569475</v>
+        <v>0.07846652869135989</v>
       </c>
       <c r="C23">
-        <v>1661.524498630019</v>
+        <v>1645.180292279784</v>
       </c>
       <c r="D23">
-        <v>1984.719198630019</v>
+        <v>1988.455692279784</v>
       </c>
       <c r="E23">
-        <v>416.7246999999999</v>
+        <v>436.8054</v>
       </c>
       <c r="F23">
-        <v>421.6947</v>
+        <v>441.7754</v>
       </c>
       <c r="G23">
         <v>98.5</v>
@@ -3173,28 +3173,28 @@
         <v>401.1</v>
       </c>
       <c r="M23">
-        <v>21.21124341</v>
+        <v>22.22130262</v>
       </c>
       <c r="N23">
-        <v>379.88875659</v>
+        <v>378.87869738</v>
       </c>
       <c r="O23">
-        <v>112.06718319405</v>
+        <v>111.7692157271</v>
       </c>
       <c r="P23">
-        <v>267.82157339595</v>
+        <v>267.1094816529</v>
       </c>
       <c r="Q23">
-        <v>270.22157339595</v>
+        <v>269.5094816529</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.09016864374138575</v>
+        <v>0.09059615216841012</v>
       </c>
       <c r="T23">
-        <v>0.6863688077596179</v>
+        <v>0.6929822271617128</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>18.90978252651149</v>
+        <v>18.05024695712461</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.07846652869135989</v>
+        <v>0.07825291382702505</v>
       </c>
       <c r="C24">
-        <v>1645.180292279784</v>
+        <v>1628.850181342659</v>
       </c>
       <c r="D24">
-        <v>1988.455692279784</v>
+        <v>1992.206281342659</v>
       </c>
       <c r="E24">
-        <v>436.8054</v>
+        <v>456.8861</v>
       </c>
       <c r="F24">
-        <v>441.7754</v>
+        <v>461.8561</v>
       </c>
       <c r="G24">
         <v>98.5</v>
@@ -3255,28 +3255,28 @@
         <v>401.1</v>
       </c>
       <c r="M24">
-        <v>22.22130262</v>
+        <v>23.23136183</v>
       </c>
       <c r="N24">
-        <v>378.87869738</v>
+        <v>377.86863817</v>
       </c>
       <c r="O24">
-        <v>111.7692157271</v>
+        <v>111.47124826015</v>
       </c>
       <c r="P24">
-        <v>267.1094816529</v>
+        <v>266.39738990985</v>
       </c>
       <c r="Q24">
-        <v>269.5094816529</v>
+        <v>268.79738990985</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.09059615216841012</v>
+        <v>0.09103476471042214</v>
       </c>
       <c r="T24">
-        <v>0.6929822271617128</v>
+        <v>0.6997674236911346</v>
       </c>
       <c r="U24">
         <v>0.0503</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>18.05024695712461</v>
+        <v>17.26545361116266</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.07825291382702505</v>
+        <v>0.07803929896269021</v>
       </c>
       <c r="C25">
-        <v>1628.850181342659</v>
+        <v>1612.534245728906</v>
       </c>
       <c r="D25">
-        <v>1992.206281342659</v>
+        <v>1995.971045728906</v>
       </c>
       <c r="E25">
-        <v>456.8861</v>
+        <v>476.9668</v>
       </c>
       <c r="F25">
-        <v>461.8561</v>
+        <v>481.9368</v>
       </c>
       <c r="G25">
         <v>98.5</v>
@@ -3337,28 +3337,28 @@
         <v>401.1</v>
       </c>
       <c r="M25">
-        <v>23.23136183</v>
+        <v>24.24142104</v>
       </c>
       <c r="N25">
-        <v>377.86863817</v>
+        <v>376.85857896</v>
       </c>
       <c r="O25">
-        <v>111.47124826015</v>
+        <v>111.1732807932</v>
       </c>
       <c r="P25">
-        <v>266.39738990985</v>
+        <v>265.6852981668001</v>
       </c>
       <c r="Q25">
-        <v>268.79738990985</v>
+        <v>268.0852981668</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.09103476471042214</v>
+        <v>0.09148491968775027</v>
       </c>
       <c r="T25">
-        <v>0.6997674236911346</v>
+        <v>0.7067311780239625</v>
       </c>
       <c r="U25">
         <v>0.0503</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>17.26545361116266</v>
+        <v>16.54605971069756</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.07803929896269021</v>
+        <v>0.07782568409835536</v>
       </c>
       <c r="C26">
-        <v>1612.534245728906</v>
+        <v>1596.232565953973</v>
       </c>
       <c r="D26">
-        <v>1995.971045728906</v>
+        <v>1999.750065953973</v>
       </c>
       <c r="E26">
-        <v>476.9667999999999</v>
+        <v>497.0475</v>
       </c>
       <c r="F26">
-        <v>481.9367999999999</v>
+        <v>502.0175</v>
       </c>
       <c r="G26">
         <v>98.5</v>
@@ -3419,28 +3419,28 @@
         <v>401.1</v>
       </c>
       <c r="M26">
-        <v>24.24142104</v>
+        <v>25.25148025</v>
       </c>
       <c r="N26">
-        <v>376.85857896</v>
+        <v>375.84851975</v>
       </c>
       <c r="O26">
-        <v>111.1732807932</v>
+        <v>110.87531332625</v>
       </c>
       <c r="P26">
-        <v>265.6852981668001</v>
+        <v>264.97320642375</v>
       </c>
       <c r="Q26">
-        <v>268.0852981668</v>
+        <v>267.37320642375</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.09148491968775027</v>
+        <v>0.09194707879780716</v>
       </c>
       <c r="T26">
-        <v>0.7067311780239625</v>
+        <v>0.7138806324723322</v>
       </c>
       <c r="U26">
         <v>0.0503</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>16.54605971069756</v>
+        <v>15.88421732226966</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.07782568409835536</v>
+        <v>0.07761206923402053</v>
       </c>
       <c r="C27">
-        <v>1596.232565953973</v>
+        <v>1579.945223144231</v>
       </c>
       <c r="D27">
-        <v>1999.750065953973</v>
+        <v>2003.54342314423</v>
       </c>
       <c r="E27">
-        <v>497.0475</v>
+        <v>517.1282</v>
       </c>
       <c r="F27">
-        <v>502.0175</v>
+        <v>522.0982</v>
       </c>
       <c r="G27">
         <v>98.5</v>
@@ -3501,28 +3501,28 @@
         <v>401.1</v>
       </c>
       <c r="M27">
-        <v>25.25148025</v>
+        <v>26.26153946</v>
       </c>
       <c r="N27">
-        <v>375.84851975</v>
+        <v>374.83846054</v>
       </c>
       <c r="O27">
-        <v>110.87531332625</v>
+        <v>110.5773458593</v>
       </c>
       <c r="P27">
-        <v>264.97320642375</v>
+        <v>264.2611146807</v>
       </c>
       <c r="Q27">
-        <v>267.37320642375</v>
+        <v>266.6611146807</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.09194707879780716</v>
+        <v>0.09242172869462234</v>
       </c>
       <c r="T27">
-        <v>0.7138806324723322</v>
+        <v>0.7212233154193067</v>
       </c>
       <c r="U27">
         <v>0.0503</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>15.88421732226966</v>
+        <v>15.27328588679774</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.07761206923402053</v>
+        <v>0.07739845436968568</v>
       </c>
       <c r="C28">
-        <v>1579.945223144231</v>
+        <v>1563.67229904278</v>
       </c>
       <c r="D28">
-        <v>2003.54342314423</v>
+        <v>2007.35119904278</v>
       </c>
       <c r="E28">
-        <v>517.1282</v>
+        <v>537.2089</v>
       </c>
       <c r="F28">
-        <v>522.0982</v>
+        <v>542.1789</v>
       </c>
       <c r="G28">
         <v>98.5</v>
@@ -3583,28 +3583,28 @@
         <v>401.1</v>
       </c>
       <c r="M28">
-        <v>26.26153946</v>
+        <v>27.27159867</v>
       </c>
       <c r="N28">
-        <v>374.83846054</v>
+        <v>373.82840133</v>
       </c>
       <c r="O28">
-        <v>110.5773458593</v>
+        <v>110.27937839235</v>
       </c>
       <c r="P28">
-        <v>264.2611146807</v>
+        <v>263.54902293765</v>
       </c>
       <c r="Q28">
-        <v>266.6611146807</v>
+        <v>265.94902293765</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.09242172869462234</v>
+        <v>0.09290938269819957</v>
       </c>
       <c r="T28">
-        <v>0.7212233154193067</v>
+        <v>0.7287671677620886</v>
       </c>
       <c r="U28">
         <v>0.0503</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>15.27328588679774</v>
+        <v>14.70760863173116</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.07739845436968568</v>
+        <v>0.07718483950535084</v>
       </c>
       <c r="C29">
-        <v>1563.67229904278</v>
+        <v>1547.413876015322</v>
       </c>
       <c r="D29">
-        <v>2007.35119904278</v>
+        <v>2011.173476015322</v>
       </c>
       <c r="E29">
-        <v>537.2089</v>
+        <v>557.2896000000001</v>
       </c>
       <c r="F29">
-        <v>542.1789</v>
+        <v>562.2596000000001</v>
       </c>
       <c r="G29">
         <v>98.5</v>
@@ -3665,28 +3665,28 @@
         <v>401.1</v>
       </c>
       <c r="M29">
-        <v>27.27159867</v>
+        <v>28.28165788</v>
       </c>
       <c r="N29">
-        <v>373.82840133</v>
+        <v>372.81834212</v>
       </c>
       <c r="O29">
-        <v>110.27937839235</v>
+        <v>109.9814109254</v>
       </c>
       <c r="P29">
-        <v>263.54902293765</v>
+        <v>262.8369311946</v>
       </c>
       <c r="Q29">
-        <v>265.94902293765</v>
+        <v>265.2369311946</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.09290938269819957</v>
+        <v>0.0934105826463206</v>
       </c>
       <c r="T29">
-        <v>0.7287671677620886</v>
+        <v>0.7365205715588367</v>
       </c>
       <c r="U29">
         <v>0.0503</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>14.70760863173116</v>
+        <v>14.18233689488362</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.07718483950535084</v>
+        <v>0.076971224641016</v>
       </c>
       <c r="C30">
-        <v>1547.413876015322</v>
+        <v>1531.170037056098</v>
       </c>
       <c r="D30">
-        <v>2011.173476015322</v>
+        <v>2015.010337056098</v>
       </c>
       <c r="E30">
-        <v>557.2896000000001</v>
+        <v>577.3703</v>
       </c>
       <c r="F30">
-        <v>562.2596000000001</v>
+        <v>582.3403000000001</v>
       </c>
       <c r="G30">
         <v>98.5</v>
@@ -3747,28 +3747,28 @@
         <v>401.1</v>
       </c>
       <c r="M30">
-        <v>28.28165788</v>
+        <v>29.29171709</v>
       </c>
       <c r="N30">
-        <v>372.81834212</v>
+        <v>371.80828291</v>
       </c>
       <c r="O30">
-        <v>109.9814109254</v>
+        <v>109.68344345845</v>
       </c>
       <c r="P30">
-        <v>262.8369311946</v>
+        <v>262.12483945155</v>
       </c>
       <c r="Q30">
-        <v>265.2369311946</v>
+        <v>264.52483945155</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.0934105826463206</v>
+        <v>0.09392590090283942</v>
       </c>
       <c r="T30">
-        <v>0.7365205715588367</v>
+        <v>0.7444923810963383</v>
       </c>
       <c r="U30">
         <v>0.0503</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>14.18233689488362</v>
+        <v>13.69329079506004</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.076971224641016</v>
+        <v>0.07675760977668114</v>
       </c>
       <c r="C31">
-        <v>1531.170037056098</v>
+        <v>1514.940865793899</v>
       </c>
       <c r="D31">
-        <v>2015.010337056098</v>
+        <v>2018.861865793899</v>
       </c>
       <c r="E31">
-        <v>577.3702999999999</v>
+        <v>597.4509999999999</v>
       </c>
       <c r="F31">
-        <v>582.3403</v>
+        <v>602.4209999999999</v>
       </c>
       <c r="G31">
         <v>98.5</v>
@@ -3829,28 +3829,28 @@
         <v>401.1</v>
       </c>
       <c r="M31">
-        <v>29.29171709</v>
+        <v>30.3017763</v>
       </c>
       <c r="N31">
-        <v>371.80828291</v>
+        <v>370.7982237000001</v>
       </c>
       <c r="O31">
-        <v>109.68344345845</v>
+        <v>109.3854759915</v>
       </c>
       <c r="P31">
-        <v>262.12483945155</v>
+        <v>261.4127477085</v>
       </c>
       <c r="Q31">
-        <v>264.52483945155</v>
+        <v>263.8127477085</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.09392590090283942</v>
+        <v>0.09445594253811593</v>
       </c>
       <c r="T31">
-        <v>0.7444923810963383</v>
+        <v>0.7526919566206256</v>
       </c>
       <c r="U31">
         <v>0.0503</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>13.69329079506005</v>
+        <v>13.23684776855805</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.07675760977668114</v>
+        <v>0.07687181991234629</v>
       </c>
       <c r="C32">
-        <v>1514.940865793899</v>
+        <v>1492.799099093347</v>
       </c>
       <c r="D32">
-        <v>2018.861865793899</v>
+        <v>2016.800799093347</v>
       </c>
       <c r="E32">
-        <v>597.4509999999999</v>
+        <v>617.5317</v>
       </c>
       <c r="F32">
-        <v>602.4209999999999</v>
+        <v>622.5017</v>
       </c>
       <c r="G32">
         <v>98.5</v>
@@ -3911,45 +3911,45 @@
         <v>401.1</v>
       </c>
       <c r="M32">
-        <v>30.3017763</v>
+        <v>32.24558806</v>
       </c>
       <c r="N32">
-        <v>370.7982237000001</v>
+        <v>368.85441194</v>
       </c>
       <c r="O32">
-        <v>109.3854759915</v>
+        <v>108.8120515223</v>
       </c>
       <c r="P32">
-        <v>261.4127477085</v>
+        <v>260.0423604177</v>
       </c>
       <c r="Q32">
-        <v>263.8127477085</v>
+        <v>262.4423604177</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.09445594253811593</v>
+        <v>0.09500134769905261</v>
       </c>
       <c r="T32">
-        <v>0.7526919566206256</v>
+        <v>0.7611292010006894</v>
       </c>
       <c r="U32">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V32">
         <v>0.295</v>
       </c>
       <c r="W32">
-        <v>0.0354615</v>
+        <v>0.036519</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y32">
-        <v>13.23684776855805</v>
+        <v>12.43891099934867</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.07687181991234629</v>
+        <v>0.07666878004801146</v>
       </c>
       <c r="C33">
-        <v>1492.799099093347</v>
+        <v>1476.38542559099</v>
       </c>
       <c r="D33">
-        <v>2016.800799093347</v>
+        <v>2020.46782559099</v>
       </c>
       <c r="E33">
-        <v>617.5317</v>
+        <v>637.6124</v>
       </c>
       <c r="F33">
-        <v>622.5017</v>
+        <v>642.5824</v>
       </c>
       <c r="G33">
         <v>98.5</v>
@@ -3993,28 +3993,28 @@
         <v>401.1</v>
       </c>
       <c r="M33">
-        <v>32.24558806</v>
+        <v>33.28576832</v>
       </c>
       <c r="N33">
-        <v>368.85441194</v>
+        <v>367.81423168</v>
       </c>
       <c r="O33">
-        <v>108.8120515223</v>
+        <v>108.5051983456</v>
       </c>
       <c r="P33">
-        <v>260.0423604177</v>
+        <v>259.3090333344001</v>
       </c>
       <c r="Q33">
-        <v>262.4423604177</v>
+        <v>261.7090333344</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.09500134769905261</v>
+        <v>0.09556279418825216</v>
       </c>
       <c r="T33">
-        <v>0.7611292010006894</v>
+        <v>0.7698145996272256</v>
       </c>
       <c r="U33">
         <v>0.0518</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>12.43891099934867</v>
+        <v>12.05019503061902</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.07666878004801146</v>
+        <v>0.07646574018367662</v>
       </c>
       <c r="C34">
-        <v>1476.38542559099</v>
+        <v>1459.98511144261</v>
       </c>
       <c r="D34">
-        <v>2020.46782559099</v>
+        <v>2024.14821144261</v>
       </c>
       <c r="E34">
-        <v>637.6124</v>
+        <v>657.6931</v>
       </c>
       <c r="F34">
-        <v>642.5824</v>
+        <v>662.6631</v>
       </c>
       <c r="G34">
         <v>98.5</v>
@@ -4075,28 +4075,28 @@
         <v>401.1</v>
       </c>
       <c r="M34">
-        <v>33.28576832</v>
+        <v>34.32594858</v>
       </c>
       <c r="N34">
-        <v>367.81423168</v>
+        <v>366.77405142</v>
       </c>
       <c r="O34">
-        <v>108.5051983456</v>
+        <v>108.1983451689</v>
       </c>
       <c r="P34">
-        <v>259.3090333344001</v>
+        <v>258.5757062511</v>
       </c>
       <c r="Q34">
-        <v>261.7090333344</v>
+        <v>260.9757062511</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.09556279418825216</v>
+        <v>0.09614100027414421</v>
       </c>
       <c r="T34">
-        <v>0.7698145996272256</v>
+        <v>0.7787592638844046</v>
       </c>
       <c r="U34">
         <v>0.0518</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>12.05019503061902</v>
+        <v>11.68503760544875</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.07646574018367662</v>
+        <v>0.07626270031934178</v>
       </c>
       <c r="C35">
-        <v>1459.98511144261</v>
+        <v>1443.598229785676</v>
       </c>
       <c r="D35">
-        <v>2024.14821144261</v>
+        <v>2027.842029785676</v>
       </c>
       <c r="E35">
-        <v>657.6931</v>
+        <v>677.7738000000001</v>
       </c>
       <c r="F35">
-        <v>662.6631</v>
+        <v>682.7438000000001</v>
       </c>
       <c r="G35">
         <v>98.5</v>
@@ -4157,28 +4157,28 @@
         <v>401.1</v>
       </c>
       <c r="M35">
-        <v>34.32594858</v>
+        <v>35.36612884</v>
       </c>
       <c r="N35">
-        <v>366.77405142</v>
+        <v>365.73387116</v>
       </c>
       <c r="O35">
-        <v>108.1983451689</v>
+        <v>107.8914919922</v>
       </c>
       <c r="P35">
-        <v>258.5757062511</v>
+        <v>257.8423791678</v>
       </c>
       <c r="Q35">
-        <v>260.9757062511</v>
+        <v>260.2423791678</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.09614100027414421</v>
+        <v>0.09673672775657846</v>
       </c>
       <c r="T35">
-        <v>0.7787592638844046</v>
+        <v>0.7879749785736196</v>
       </c>
       <c r="U35">
         <v>0.0518</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>11.68503760544875</v>
+        <v>11.3413600288179</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.07626270031934178</v>
+        <v>0.07605966045500694</v>
       </c>
       <c r="C36">
-        <v>1443.598229785676</v>
+        <v>1427.224854292502</v>
       </c>
       <c r="D36">
-        <v>2027.842029785676</v>
+        <v>2031.549354292502</v>
       </c>
       <c r="E36">
-        <v>677.7738000000001</v>
+        <v>697.8545</v>
       </c>
       <c r="F36">
-        <v>682.7438000000001</v>
+        <v>702.8245000000001</v>
       </c>
       <c r="G36">
         <v>98.5</v>
@@ -4239,28 +4239,28 @@
         <v>401.1</v>
       </c>
       <c r="M36">
-        <v>35.36612884</v>
+        <v>36.4063091</v>
       </c>
       <c r="N36">
-        <v>365.73387116</v>
+        <v>364.6936909</v>
       </c>
       <c r="O36">
-        <v>107.8914919922</v>
+        <v>107.5846388155</v>
       </c>
       <c r="P36">
-        <v>257.8423791678</v>
+        <v>257.1090520845</v>
       </c>
       <c r="Q36">
-        <v>260.2423791678</v>
+        <v>259.5090520845</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.09673672775657846</v>
+        <v>0.09735078531539529</v>
       </c>
       <c r="T36">
-        <v>0.7879749785736196</v>
+        <v>0.7974742537148103</v>
       </c>
       <c r="U36">
         <v>0.0518</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>11.3413600288179</v>
+        <v>11.01732117085168</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.07605966045500694</v>
+        <v>0.07585662059067209</v>
       </c>
       <c r="C37">
-        <v>1427.224854292502</v>
+        <v>1410.865059175143</v>
       </c>
       <c r="D37">
-        <v>2031.549354292502</v>
+        <v>2035.270259175144</v>
       </c>
       <c r="E37">
-        <v>697.8545</v>
+        <v>717.9352</v>
       </c>
       <c r="F37">
-        <v>702.8245000000001</v>
+        <v>722.9052</v>
       </c>
       <c r="G37">
         <v>98.5</v>
@@ -4321,28 +4321,28 @@
         <v>401.1</v>
       </c>
       <c r="M37">
-        <v>36.4063091</v>
+        <v>37.44648936</v>
       </c>
       <c r="N37">
-        <v>364.6936909</v>
+        <v>363.65351064</v>
       </c>
       <c r="O37">
-        <v>107.5846388155</v>
+        <v>107.2777856388</v>
       </c>
       <c r="P37">
-        <v>257.1090520845</v>
+        <v>256.3757250012</v>
       </c>
       <c r="Q37">
-        <v>259.5090520845</v>
+        <v>258.7757250012</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.09735078531539529</v>
+        <v>0.09798403217292515</v>
       </c>
       <c r="T37">
-        <v>0.7974742537148103</v>
+        <v>0.8072703812041632</v>
       </c>
       <c r="U37">
         <v>0.0518</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>11.01732117085168</v>
+        <v>10.71128447166135</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.07585662059067208</v>
+        <v>0.07565358072633724</v>
       </c>
       <c r="C38">
-        <v>1410.865059175144</v>
+        <v>1394.518919190347</v>
       </c>
       <c r="D38">
-        <v>2035.270259175144</v>
+        <v>2039.004819190347</v>
       </c>
       <c r="E38">
-        <v>717.9351999999999</v>
+        <v>738.0159</v>
       </c>
       <c r="F38">
-        <v>722.9051999999999</v>
+        <v>742.9859</v>
       </c>
       <c r="G38">
         <v>98.5</v>
@@ -4403,28 +4403,28 @@
         <v>401.1</v>
       </c>
       <c r="M38">
-        <v>37.44648935999999</v>
+        <v>38.48666962</v>
       </c>
       <c r="N38">
-        <v>363.65351064</v>
+        <v>362.61333038</v>
       </c>
       <c r="O38">
-        <v>107.2777856388</v>
+        <v>106.9709324621</v>
       </c>
       <c r="P38">
-        <v>256.3757250012</v>
+        <v>255.6423979179</v>
       </c>
       <c r="Q38">
-        <v>258.7757250012</v>
+        <v>258.0423979179</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.09798403217292515</v>
+        <v>0.09863738210529721</v>
       </c>
       <c r="T38">
-        <v>0.8072703812041631</v>
+        <v>0.8173774968677812</v>
       </c>
       <c r="U38">
         <v>0.0518</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>10.71128447166135</v>
+        <v>10.42179029675158</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.07565358072633724</v>
+        <v>0.0754505408620024</v>
       </c>
       <c r="C39">
-        <v>1394.518919190347</v>
+        <v>1378.186509644562</v>
       </c>
       <c r="D39">
-        <v>2039.004819190347</v>
+        <v>2042.753109644562</v>
       </c>
       <c r="E39">
-        <v>738.0159</v>
+        <v>758.0966</v>
       </c>
       <c r="F39">
-        <v>742.9859</v>
+        <v>763.0666</v>
       </c>
       <c r="G39">
         <v>98.5</v>
@@ -4485,28 +4485,28 @@
         <v>401.1</v>
       </c>
       <c r="M39">
-        <v>38.48666962</v>
+        <v>39.52684988</v>
       </c>
       <c r="N39">
-        <v>362.61333038</v>
+        <v>361.57315012</v>
       </c>
       <c r="O39">
-        <v>106.9709324621</v>
+        <v>106.6640792854</v>
       </c>
       <c r="P39">
-        <v>255.6423979179</v>
+        <v>254.9090708346</v>
       </c>
       <c r="Q39">
-        <v>258.0423979179</v>
+        <v>257.3090708346</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.09863738210529721</v>
+        <v>0.09931180784193935</v>
       </c>
       <c r="T39">
-        <v>0.8173774968677812</v>
+        <v>0.8278106485205482</v>
       </c>
       <c r="U39">
         <v>0.0518</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>10.42179029675158</v>
+        <v>10.14753265736339</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.0754505408620024</v>
+        <v>0.07524750099766757</v>
       </c>
       <c r="C40">
-        <v>1378.186509644562</v>
+        <v>1361.867906398994</v>
       </c>
       <c r="D40">
-        <v>2042.753109644562</v>
+        <v>2046.515206398995</v>
       </c>
       <c r="E40">
-        <v>758.0966</v>
+        <v>778.1772999999999</v>
       </c>
       <c r="F40">
-        <v>763.0666</v>
+        <v>783.1473</v>
       </c>
       <c r="G40">
         <v>98.5</v>
@@ -4567,28 +4567,28 @@
         <v>401.1</v>
       </c>
       <c r="M40">
-        <v>39.52684988</v>
+        <v>40.56703014</v>
       </c>
       <c r="N40">
-        <v>361.57315012</v>
+        <v>360.53296986</v>
       </c>
       <c r="O40">
-        <v>106.6640792854</v>
+        <v>106.3572261087</v>
       </c>
       <c r="P40">
-        <v>254.9090708346</v>
+        <v>254.1757437513</v>
       </c>
       <c r="Q40">
-        <v>257.3090708346</v>
+        <v>256.5757437513</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.09931180784193935</v>
+        <v>0.1000083458978157</v>
       </c>
       <c r="T40">
-        <v>0.8278106485205482</v>
+        <v>0.8385858707193078</v>
       </c>
       <c r="U40">
         <v>0.0518</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>10.14753265736339</v>
+        <v>9.887339512302786</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.07524750099766757</v>
+        <v>0.07552386113333272</v>
       </c>
       <c r="C41">
-        <v>1361.867906398994</v>
+        <v>1336.669965754858</v>
       </c>
       <c r="D41">
-        <v>2046.515206398995</v>
+        <v>2041.397965754858</v>
       </c>
       <c r="E41">
-        <v>778.1772999999999</v>
+        <v>798.258</v>
       </c>
       <c r="F41">
-        <v>783.1473</v>
+        <v>803.2280000000001</v>
       </c>
       <c r="G41">
         <v>98.5</v>
@@ -4649,45 +4649,45 @@
         <v>401.1</v>
       </c>
       <c r="M41">
-        <v>40.56703014</v>
+        <v>42.972698</v>
       </c>
       <c r="N41">
-        <v>360.53296986</v>
+        <v>358.127302</v>
       </c>
       <c r="O41">
-        <v>106.3572261087</v>
+        <v>105.64755409</v>
       </c>
       <c r="P41">
-        <v>254.1757437513</v>
+        <v>252.47974791</v>
       </c>
       <c r="Q41">
-        <v>256.5757437513</v>
+        <v>254.87974791</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1000083458978157</v>
+        <v>0.1007281018888879</v>
       </c>
       <c r="T41">
-        <v>0.8385858707193078</v>
+        <v>0.8497202669913591</v>
       </c>
       <c r="U41">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V41">
         <v>0.295</v>
       </c>
       <c r="W41">
-        <v>0.036519</v>
+        <v>0.0377175</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y41">
-        <v>9.887339512302786</v>
+        <v>9.333833309698173</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.07552386113333272</v>
+        <v>0.07533280626899787</v>
       </c>
       <c r="C42">
-        <v>1336.669965754858</v>
+        <v>1320.124210513258</v>
       </c>
       <c r="D42">
-        <v>2041.397965754858</v>
+        <v>2044.932910513258</v>
       </c>
       <c r="E42">
-        <v>798.258</v>
+        <v>818.3387</v>
       </c>
       <c r="F42">
-        <v>803.2280000000001</v>
+        <v>823.3087</v>
       </c>
       <c r="G42">
         <v>98.5</v>
@@ -4731,28 +4731,28 @@
         <v>401.1</v>
       </c>
       <c r="M42">
-        <v>42.972698</v>
+        <v>44.04701545</v>
       </c>
       <c r="N42">
-        <v>358.127302</v>
+        <v>357.05298455</v>
       </c>
       <c r="O42">
-        <v>105.64755409</v>
+        <v>105.33063044225</v>
       </c>
       <c r="P42">
-        <v>252.47974791</v>
+        <v>251.72235410775</v>
       </c>
       <c r="Q42">
-        <v>254.87974791</v>
+        <v>254.12235410775</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1007281018888879</v>
+        <v>0.101472256388132</v>
       </c>
       <c r="T42">
-        <v>0.8497202669913591</v>
+        <v>0.8612321004251748</v>
       </c>
       <c r="U42">
         <v>0.0535</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>9.333833309698173</v>
+        <v>9.106178838729923</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.07533280626899787</v>
+        <v>0.07514175140466303</v>
       </c>
       <c r="C43">
-        <v>1320.124210513258</v>
+        <v>1303.590718936406</v>
       </c>
       <c r="D43">
-        <v>2044.932910513258</v>
+        <v>2048.480118936406</v>
       </c>
       <c r="E43">
-        <v>818.3387</v>
+        <v>838.4194</v>
       </c>
       <c r="F43">
-        <v>823.3087</v>
+        <v>843.3894</v>
       </c>
       <c r="G43">
         <v>98.5</v>
@@ -4813,28 +4813,28 @@
         <v>401.1</v>
       </c>
       <c r="M43">
-        <v>44.04701545</v>
+        <v>45.1213329</v>
       </c>
       <c r="N43">
-        <v>357.05298455</v>
+        <v>355.9786671000001</v>
       </c>
       <c r="O43">
-        <v>105.33063044225</v>
+        <v>105.0137067945</v>
       </c>
       <c r="P43">
-        <v>251.72235410775</v>
+        <v>250.9649603055</v>
       </c>
       <c r="Q43">
-        <v>254.12235410775</v>
+        <v>253.3649603055</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.101472256388132</v>
+        <v>0.1022420713873501</v>
       </c>
       <c r="T43">
-        <v>0.8612321004251748</v>
+        <v>0.8731408936325705</v>
       </c>
       <c r="U43">
         <v>0.0535</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>9.106178838729923</v>
+        <v>8.889365056855404</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.07514175140466305</v>
+        <v>0.0749506965403282</v>
       </c>
       <c r="C44">
-        <v>1303.590718936406</v>
+        <v>1287.069554954073</v>
       </c>
       <c r="D44">
-        <v>2048.480118936406</v>
+        <v>2052.039654954073</v>
       </c>
       <c r="E44">
-        <v>838.4193999999999</v>
+        <v>858.5001</v>
       </c>
       <c r="F44">
-        <v>843.3893999999999</v>
+        <v>863.4701</v>
       </c>
       <c r="G44">
         <v>98.5</v>
@@ -4895,28 +4895,28 @@
         <v>401.1</v>
       </c>
       <c r="M44">
-        <v>45.12133289999999</v>
+        <v>46.19565035</v>
       </c>
       <c r="N44">
-        <v>355.9786671000001</v>
+        <v>354.90434965</v>
       </c>
       <c r="O44">
-        <v>105.0137067945</v>
+        <v>104.69678314675</v>
       </c>
       <c r="P44">
-        <v>250.9649603055</v>
+        <v>250.20756650325</v>
       </c>
       <c r="Q44">
-        <v>253.3649603055</v>
+        <v>252.60756650325</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1022420713873501</v>
+        <v>0.1030388974391723</v>
       </c>
       <c r="T44">
-        <v>0.8731408936325705</v>
+        <v>0.8854675392332081</v>
       </c>
       <c r="U44">
         <v>0.0535</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>8.889365056855404</v>
+        <v>8.682635636928532</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.0749506965403282</v>
+        <v>0.07475964167599336</v>
       </c>
       <c r="C45">
-        <v>1287.069554954073</v>
+        <v>1270.560782941157</v>
       </c>
       <c r="D45">
-        <v>2052.039654954073</v>
+        <v>2055.611582941157</v>
       </c>
       <c r="E45">
-        <v>858.5001</v>
+        <v>878.5808</v>
       </c>
       <c r="F45">
-        <v>863.4701</v>
+        <v>883.5508</v>
       </c>
       <c r="G45">
         <v>98.5</v>
@@ -4977,28 +4977,28 @@
         <v>401.1</v>
       </c>
       <c r="M45">
-        <v>46.19565035</v>
+        <v>47.2699678</v>
       </c>
       <c r="N45">
-        <v>354.90434965</v>
+        <v>353.8300322</v>
       </c>
       <c r="O45">
-        <v>104.69678314675</v>
+        <v>104.379859499</v>
       </c>
       <c r="P45">
-        <v>250.20756650325</v>
+        <v>249.450172701</v>
       </c>
       <c r="Q45">
-        <v>252.60756650325</v>
+        <v>251.850172701</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1030388974391723</v>
+        <v>0.1038641815642738</v>
       </c>
       <c r="T45">
-        <v>0.8854675392332081</v>
+        <v>0.8982344221767258</v>
       </c>
       <c r="U45">
         <v>0.0535</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>8.682635636928532</v>
+        <v>8.485303008816519</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.07475964167599336</v>
+        <v>0.07456858681165851</v>
       </c>
       <c r="C46">
-        <v>1270.560782941157</v>
+        <v>1254.064467721558</v>
       </c>
       <c r="D46">
-        <v>2055.611582941157</v>
+        <v>2059.195967721558</v>
       </c>
       <c r="E46">
-        <v>878.5808</v>
+        <v>898.6614999999999</v>
       </c>
       <c r="F46">
-        <v>883.5508</v>
+        <v>903.6315</v>
       </c>
       <c r="G46">
         <v>98.5</v>
@@ -5059,28 +5059,28 @@
         <v>401.1</v>
       </c>
       <c r="M46">
-        <v>47.2699678</v>
+        <v>48.34428525</v>
       </c>
       <c r="N46">
-        <v>353.8300322</v>
+        <v>352.75571475</v>
       </c>
       <c r="O46">
-        <v>104.379859499</v>
+        <v>104.06293585125</v>
       </c>
       <c r="P46">
-        <v>249.450172701</v>
+        <v>248.69277889875</v>
       </c>
       <c r="Q46">
-        <v>251.850172701</v>
+        <v>251.09277889875</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1038641815642738</v>
+        <v>0.1047194760211973</v>
       </c>
       <c r="T46">
-        <v>0.8982344221767258</v>
+        <v>0.9114655554090983</v>
       </c>
       <c r="U46">
         <v>0.0535</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>8.485303008816519</v>
+        <v>8.296740719731709</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.07456858681165851</v>
+        <v>0.07437753194732367</v>
       </c>
       <c r="C47">
-        <v>1254.064467721558</v>
+        <v>1237.580674572099</v>
       </c>
       <c r="D47">
-        <v>2059.195967721558</v>
+        <v>2062.792874572099</v>
       </c>
       <c r="E47">
-        <v>898.6614999999999</v>
+        <v>918.7422</v>
       </c>
       <c r="F47">
-        <v>903.6315</v>
+        <v>923.7122000000001</v>
       </c>
       <c r="G47">
         <v>98.5</v>
@@ -5141,28 +5141,28 @@
         <v>401.1</v>
       </c>
       <c r="M47">
-        <v>48.34428525</v>
+        <v>49.4186027</v>
       </c>
       <c r="N47">
-        <v>352.75571475</v>
+        <v>351.6813973</v>
       </c>
       <c r="O47">
-        <v>104.06293585125</v>
+        <v>103.7460122035</v>
       </c>
       <c r="P47">
-        <v>248.69277889875</v>
+        <v>247.9353850965</v>
       </c>
       <c r="Q47">
-        <v>251.09277889875</v>
+        <v>250.3353850965</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1047194760211973</v>
+        <v>0.1056064480505994</v>
       </c>
       <c r="T47">
-        <v>0.9114655554090983</v>
+        <v>0.9251867306130407</v>
       </c>
       <c r="U47">
         <v>0.0535</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>8.296740719731709</v>
+        <v>8.116376791041889</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.07437753194732367</v>
+        <v>0.07418647708298882</v>
       </c>
       <c r="C48">
-        <v>1237.580674572099</v>
+        <v>1221.109469226496</v>
       </c>
       <c r="D48">
-        <v>2062.792874572099</v>
+        <v>2066.402369226496</v>
       </c>
       <c r="E48">
-        <v>918.7422</v>
+        <v>938.8229</v>
       </c>
       <c r="F48">
-        <v>923.7122000000001</v>
+        <v>943.7929</v>
       </c>
       <c r="G48">
         <v>98.5</v>
@@ -5223,28 +5223,28 @@
         <v>401.1</v>
       </c>
       <c r="M48">
-        <v>49.4186027</v>
+        <v>50.49292015</v>
       </c>
       <c r="N48">
-        <v>351.6813973</v>
+        <v>350.60707985</v>
       </c>
       <c r="O48">
-        <v>103.7460122035</v>
+        <v>103.42908855575</v>
       </c>
       <c r="P48">
-        <v>247.9353850965</v>
+        <v>247.17799129425</v>
       </c>
       <c r="Q48">
-        <v>250.3353850965</v>
+        <v>249.57799129425</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1056064480505994</v>
+        <v>0.1065268907226204</v>
       </c>
       <c r="T48">
-        <v>0.9251867306130407</v>
+        <v>0.939425686013358</v>
       </c>
       <c r="U48">
         <v>0.0535</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>8.116376791041889</v>
+        <v>7.94368792314738</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.07418647708298882</v>
+        <v>0.07399542221865398</v>
       </c>
       <c r="C49">
-        <v>1221.109469226496</v>
+        <v>1204.650917879354</v>
       </c>
       <c r="D49">
-        <v>2066.402369226496</v>
+        <v>2070.024517879354</v>
       </c>
       <c r="E49">
-        <v>938.8229</v>
+        <v>958.9036</v>
       </c>
       <c r="F49">
-        <v>943.7929</v>
+        <v>963.8736</v>
       </c>
       <c r="G49">
         <v>98.5</v>
@@ -5305,28 +5305,28 @@
         <v>401.1</v>
       </c>
       <c r="M49">
-        <v>50.49292015</v>
+        <v>51.5672376</v>
       </c>
       <c r="N49">
-        <v>350.60707985</v>
+        <v>349.5327624</v>
       </c>
       <c r="O49">
-        <v>103.42908855575</v>
+        <v>103.112164908</v>
       </c>
       <c r="P49">
-        <v>247.17799129425</v>
+        <v>246.420597492</v>
       </c>
       <c r="Q49">
-        <v>249.57799129425</v>
+        <v>248.820597492</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1065268907226204</v>
+        <v>0.107482735035873</v>
       </c>
       <c r="T49">
-        <v>0.939425686013358</v>
+        <v>0.9542122935444565</v>
       </c>
       <c r="U49">
         <v>0.0535</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>7.94368792314738</v>
+        <v>7.778194424748477</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.07399542221865398</v>
+        <v>0.07380436735431913</v>
       </c>
       <c r="C50">
-        <v>1204.650917879354</v>
+        <v>1188.205087190217</v>
       </c>
       <c r="D50">
-        <v>2070.024517879354</v>
+        <v>2073.659387190217</v>
       </c>
       <c r="E50">
-        <v>958.9035999999999</v>
+        <v>978.9843</v>
       </c>
       <c r="F50">
-        <v>963.8735999999999</v>
+        <v>983.9543</v>
       </c>
       <c r="G50">
         <v>98.5</v>
@@ -5387,28 +5387,28 @@
         <v>401.1</v>
       </c>
       <c r="M50">
-        <v>51.56723759999999</v>
+        <v>52.64155505</v>
       </c>
       <c r="N50">
-        <v>349.5327624</v>
+        <v>348.45844495</v>
       </c>
       <c r="O50">
-        <v>103.112164908</v>
+        <v>102.79524126025</v>
       </c>
       <c r="P50">
-        <v>246.420597492</v>
+        <v>245.66320368975</v>
       </c>
       <c r="Q50">
-        <v>248.820597492</v>
+        <v>248.06320368975</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.107482735035873</v>
+        <v>0.1084760634398414</v>
       </c>
       <c r="T50">
-        <v>0.9542122935444565</v>
+        <v>0.969578768037559</v>
       </c>
       <c r="U50">
         <v>0.0535</v>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>7.778194424748478</v>
+        <v>7.619455763018916</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.07380436735431913</v>
+        <v>0.07389531248998429</v>
       </c>
       <c r="C51">
-        <v>1188.205087190217</v>
+        <v>1166.392541272024</v>
       </c>
       <c r="D51">
-        <v>2073.659387190217</v>
+        <v>2071.927541272024</v>
       </c>
       <c r="E51">
-        <v>978.9843</v>
+        <v>999.0649999999999</v>
       </c>
       <c r="F51">
-        <v>983.9543</v>
+        <v>1004.035</v>
       </c>
       <c r="G51">
         <v>98.5</v>
@@ -5469,45 +5469,45 @@
         <v>401.1</v>
       </c>
       <c r="M51">
-        <v>52.64155505</v>
+        <v>54.5191005</v>
       </c>
       <c r="N51">
-        <v>348.45844495</v>
+        <v>346.5808995</v>
       </c>
       <c r="O51">
-        <v>102.79524126025</v>
+        <v>102.2413653525</v>
       </c>
       <c r="P51">
-        <v>245.66320368975</v>
+        <v>244.3395341475</v>
       </c>
       <c r="Q51">
-        <v>248.06320368975</v>
+        <v>246.7395341475001</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1084760634398414</v>
+        <v>0.1095091249799686</v>
       </c>
       <c r="T51">
-        <v>0.969578768037559</v>
+        <v>0.9855599015103859</v>
       </c>
       <c r="U51">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V51">
         <v>0.295</v>
       </c>
       <c r="W51">
-        <v>0.0377175</v>
+        <v>0.0382815</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y51">
-        <v>7.619455763018916</v>
+        <v>7.357054616115686</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.07389531248998429</v>
+        <v>0.07370989762564945</v>
       </c>
       <c r="C52">
-        <v>1166.392541272024</v>
+        <v>1149.845719380229</v>
       </c>
       <c r="D52">
-        <v>2071.927541272024</v>
+        <v>2075.461419380229</v>
       </c>
       <c r="E52">
-        <v>999.0649999999999</v>
+        <v>1019.1457</v>
       </c>
       <c r="F52">
-        <v>1004.035</v>
+        <v>1024.1157</v>
       </c>
       <c r="G52">
         <v>98.5</v>
@@ -5551,28 +5551,28 @@
         <v>401.1</v>
       </c>
       <c r="M52">
-        <v>54.5191005</v>
+        <v>55.60948251000001</v>
       </c>
       <c r="N52">
-        <v>346.5808995</v>
+        <v>345.49051749</v>
       </c>
       <c r="O52">
-        <v>102.2413653525</v>
+        <v>101.91970265955</v>
       </c>
       <c r="P52">
-        <v>244.3395341475</v>
+        <v>243.57081483045</v>
       </c>
       <c r="Q52">
-        <v>246.7395341475001</v>
+        <v>245.97081483045</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1095091249799686</v>
+        <v>0.1105843522972438</v>
       </c>
       <c r="T52">
-        <v>0.9855599015103859</v>
+        <v>1.002193326145369</v>
       </c>
       <c r="U52">
         <v>0.0543</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>7.357054616115686</v>
+        <v>7.212798643250672</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.07370989762564945</v>
+        <v>0.0735244827613146</v>
       </c>
       <c r="C53">
-        <v>1149.845719380229</v>
+        <v>1133.310972844017</v>
       </c>
       <c r="D53">
-        <v>2075.461419380229</v>
+        <v>2079.007372844017</v>
       </c>
       <c r="E53">
-        <v>1019.1457</v>
+        <v>1039.2264</v>
       </c>
       <c r="F53">
-        <v>1024.1157</v>
+        <v>1044.1964</v>
       </c>
       <c r="G53">
         <v>98.5</v>
@@ -5633,28 +5633,28 @@
         <v>401.1</v>
       </c>
       <c r="M53">
-        <v>55.60948251000001</v>
+        <v>56.69986452000001</v>
       </c>
       <c r="N53">
-        <v>345.49051749</v>
+        <v>344.40013548</v>
       </c>
       <c r="O53">
-        <v>101.91970265955</v>
+        <v>101.5980399666</v>
       </c>
       <c r="P53">
-        <v>243.57081483045</v>
+        <v>242.8020955134</v>
       </c>
       <c r="Q53">
-        <v>245.97081483045</v>
+        <v>245.2020955134</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1105843522972438</v>
+        <v>0.1117043807527388</v>
       </c>
       <c r="T53">
-        <v>1.002193326145369</v>
+        <v>1.019519810140143</v>
       </c>
       <c r="U53">
         <v>0.0543</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>7.212798643250672</v>
+        <v>7.074090977034313</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.0735244827613146</v>
+        <v>0.07333906789697976</v>
       </c>
       <c r="C54">
-        <v>1133.310972844017</v>
+        <v>1116.788363662031</v>
       </c>
       <c r="D54">
-        <v>2079.007372844017</v>
+        <v>2082.565463662031</v>
       </c>
       <c r="E54">
-        <v>1039.2264</v>
+        <v>1059.3071</v>
       </c>
       <c r="F54">
-        <v>1044.1964</v>
+        <v>1064.2771</v>
       </c>
       <c r="G54">
         <v>98.5</v>
@@ -5715,28 +5715,28 @@
         <v>401.1</v>
       </c>
       <c r="M54">
-        <v>56.69986452000001</v>
+        <v>57.79024653</v>
       </c>
       <c r="N54">
-        <v>344.40013548</v>
+        <v>343.30975347</v>
       </c>
       <c r="O54">
-        <v>101.5980399666</v>
+        <v>101.27637727365</v>
       </c>
       <c r="P54">
-        <v>242.8020955134</v>
+        <v>242.03337619635</v>
       </c>
       <c r="Q54">
-        <v>245.2020955134</v>
+        <v>244.4333761963501</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1117043807527388</v>
+        <v>0.112872069993574</v>
       </c>
       <c r="T54">
-        <v>1.019519810140143</v>
+        <v>1.037583591326183</v>
       </c>
       <c r="U54">
         <v>0.0543</v>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>7.074090977034313</v>
+        <v>6.940617562373289</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.07333906789697976</v>
+        <v>0.07315365303264493</v>
       </c>
       <c r="C55">
-        <v>1116.788363662031</v>
+        <v>1100.277954258067</v>
       </c>
       <c r="D55">
-        <v>2082.565463662031</v>
+        <v>2086.135754258067</v>
       </c>
       <c r="E55">
-        <v>1059.3071</v>
+        <v>1079.3878</v>
       </c>
       <c r="F55">
-        <v>1064.2771</v>
+        <v>1084.3578</v>
       </c>
       <c r="G55">
         <v>98.5</v>
@@ -5797,28 +5797,28 @@
         <v>401.1</v>
       </c>
       <c r="M55">
-        <v>57.79024653</v>
+        <v>58.88062854</v>
       </c>
       <c r="N55">
-        <v>343.30975347</v>
+        <v>342.21937146</v>
       </c>
       <c r="O55">
-        <v>101.27637727365</v>
+        <v>100.9547145807</v>
       </c>
       <c r="P55">
-        <v>242.03337619635</v>
+        <v>241.2646568793</v>
       </c>
       <c r="Q55">
-        <v>244.4333761963501</v>
+        <v>243.6646568793001</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.112872069993574</v>
+        <v>0.1140905283318368</v>
       </c>
       <c r="T55">
-        <v>1.037583591326183</v>
+        <v>1.056432754302922</v>
       </c>
       <c r="U55">
         <v>0.0543</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>6.940617562373289</v>
+        <v>6.812087607514524</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.07315365303264493</v>
+        <v>0.07296823816831008</v>
       </c>
       <c r="C56">
-        <v>1100.277954258067</v>
+        <v>1083.779807484729</v>
       </c>
       <c r="D56">
-        <v>2086.135754258067</v>
+        <v>2089.718307484729</v>
       </c>
       <c r="E56">
-        <v>1079.3878</v>
+        <v>1099.4685</v>
       </c>
       <c r="F56">
-        <v>1084.3578</v>
+        <v>1104.4385</v>
       </c>
       <c r="G56">
         <v>98.5</v>
@@ -5879,28 +5879,28 @@
         <v>401.1</v>
       </c>
       <c r="M56">
-        <v>58.88062854</v>
+        <v>59.97101055</v>
       </c>
       <c r="N56">
-        <v>342.21937146</v>
+        <v>341.12898945</v>
       </c>
       <c r="O56">
-        <v>100.9547145807</v>
+        <v>100.63305188775</v>
       </c>
       <c r="P56">
-        <v>241.2646568793</v>
+        <v>240.49593756225</v>
       </c>
       <c r="Q56">
-        <v>243.6646568793001</v>
+        <v>242.89593756225</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1140905283318368</v>
+        <v>0.1153631403740224</v>
       </c>
       <c r="T56">
-        <v>1.056432754302922</v>
+        <v>1.076119657856404</v>
       </c>
       <c r="U56">
         <v>0.0543</v>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>6.812087607514524</v>
+        <v>6.688231469196078</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.07296823816831008</v>
+        <v>0.07278282330397524</v>
       </c>
       <c r="C57">
-        <v>1083.779807484729</v>
+        <v>1067.293986627113</v>
       </c>
       <c r="D57">
-        <v>2089.718307484729</v>
+        <v>2093.313186627113</v>
       </c>
       <c r="E57">
-        <v>1099.4685</v>
+        <v>1119.5492</v>
       </c>
       <c r="F57">
-        <v>1104.4385</v>
+        <v>1124.5192</v>
       </c>
       <c r="G57">
         <v>98.5</v>
@@ -5961,28 +5961,28 @@
         <v>401.1</v>
       </c>
       <c r="M57">
-        <v>59.97101055</v>
+        <v>61.06139256000001</v>
       </c>
       <c r="N57">
-        <v>341.12898945</v>
+        <v>340.03860744</v>
       </c>
       <c r="O57">
-        <v>100.63305188775</v>
+        <v>100.3113891948</v>
       </c>
       <c r="P57">
-        <v>240.49593756225</v>
+        <v>239.7272182452</v>
       </c>
       <c r="Q57">
-        <v>242.89593756225</v>
+        <v>242.1272182452</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1153631403740224</v>
+        <v>0.1166935984181255</v>
       </c>
       <c r="T57">
-        <v>1.076119657856404</v>
+        <v>1.096701420662317</v>
       </c>
       <c r="U57">
         <v>0.0543</v>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>6.688231469196078</v>
+        <v>6.568798764389005</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.07278282330397524</v>
+        <v>0.07259740843964038</v>
       </c>
       <c r="C58">
-        <v>1067.293986627113</v>
+        <v>1050.820555406538</v>
       </c>
       <c r="D58">
-        <v>2093.313186627113</v>
+        <v>2096.920455406538</v>
       </c>
       <c r="E58">
-        <v>1119.5492</v>
+        <v>1139.6299</v>
       </c>
       <c r="F58">
-        <v>1124.5192</v>
+        <v>1144.5999</v>
       </c>
       <c r="G58">
         <v>98.5</v>
@@ -6043,28 +6043,28 @@
         <v>401.1</v>
       </c>
       <c r="M58">
-        <v>61.06139256000001</v>
+        <v>62.15177457000001</v>
       </c>
       <c r="N58">
-        <v>340.03860744</v>
+        <v>338.94822543</v>
       </c>
       <c r="O58">
-        <v>100.3113891948</v>
+        <v>99.98972650185</v>
       </c>
       <c r="P58">
-        <v>239.7272182452</v>
+        <v>238.95849892815</v>
       </c>
       <c r="Q58">
-        <v>242.1272182452</v>
+        <v>241.3584989281501</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1166935984181255</v>
+        <v>0.1180859382317218</v>
       </c>
       <c r="T58">
-        <v>1.096701420662317</v>
+        <v>1.118240474761528</v>
       </c>
       <c r="U58">
         <v>0.0543</v>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>6.568798764389005</v>
+        <v>6.453556680803233</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.07259740843964038</v>
+        <v>0.07241199357530553</v>
       </c>
       <c r="C59">
-        <v>1050.820555406538</v>
+        <v>1034.359577984304</v>
       </c>
       <c r="D59">
-        <v>2096.920455406538</v>
+        <v>2100.540177984304</v>
       </c>
       <c r="E59">
-        <v>1139.6299</v>
+        <v>1159.7106</v>
       </c>
       <c r="F59">
-        <v>1144.5999</v>
+        <v>1164.6806</v>
       </c>
       <c r="G59">
         <v>98.5</v>
@@ -6125,28 +6125,28 @@
         <v>401.1</v>
       </c>
       <c r="M59">
-        <v>62.15177457000001</v>
+        <v>63.24215658000001</v>
       </c>
       <c r="N59">
-        <v>338.94822543</v>
+        <v>337.85784342</v>
       </c>
       <c r="O59">
-        <v>99.98972650185</v>
+        <v>99.66806380889999</v>
       </c>
       <c r="P59">
-        <v>238.95849892815</v>
+        <v>238.1897796111</v>
       </c>
       <c r="Q59">
-        <v>241.3584989281501</v>
+        <v>240.5897796111</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1180859382317218</v>
+        <v>0.1195445799412037</v>
       </c>
       <c r="T59">
-        <v>1.118240474761528</v>
+        <v>1.140805198103559</v>
       </c>
       <c r="U59">
         <v>0.0543</v>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>6.453556680803233</v>
+        <v>6.342288462168694</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.07241199357530555</v>
+        <v>0.07222657871097071</v>
       </c>
       <c r="C60">
-        <v>1034.359577984304</v>
+        <v>1017.911118965502</v>
       </c>
       <c r="D60">
-        <v>2100.540177984304</v>
+        <v>2104.172418965502</v>
       </c>
       <c r="E60">
-        <v>1159.7106</v>
+        <v>1179.7913</v>
       </c>
       <c r="F60">
-        <v>1164.6806</v>
+        <v>1184.7613</v>
       </c>
       <c r="G60">
         <v>98.5</v>
@@ -6207,28 +6207,28 @@
         <v>401.1</v>
       </c>
       <c r="M60">
-        <v>63.24215658</v>
+        <v>64.33253859</v>
       </c>
       <c r="N60">
-        <v>337.85784342</v>
+        <v>336.76746141</v>
       </c>
       <c r="O60">
-        <v>99.66806380889999</v>
+        <v>99.34640111595</v>
       </c>
       <c r="P60">
-        <v>238.1897796111</v>
+        <v>237.42106029405</v>
       </c>
       <c r="Q60">
-        <v>240.5897796111</v>
+        <v>239.82106029405</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1195445799412037</v>
+        <v>0.1210743749048066</v>
       </c>
       <c r="T60">
-        <v>1.140805198103559</v>
+        <v>1.164470639657397</v>
       </c>
       <c r="U60">
         <v>0.0543</v>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>6.342288462168694</v>
+        <v>6.234792047555667</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.07222657871097071</v>
+        <v>0.07204116384663586</v>
       </c>
       <c r="C61">
-        <v>1017.911118965502</v>
+        <v>1001.475243402858</v>
       </c>
       <c r="D61">
-        <v>2104.172418965502</v>
+        <v>2107.817243402858</v>
       </c>
       <c r="E61">
-        <v>1179.7913</v>
+        <v>1199.872</v>
       </c>
       <c r="F61">
-        <v>1184.7613</v>
+        <v>1204.842</v>
       </c>
       <c r="G61">
         <v>98.5</v>
@@ -6289,28 +6289,28 @@
         <v>401.1</v>
       </c>
       <c r="M61">
-        <v>64.33253859</v>
+        <v>65.4229206</v>
       </c>
       <c r="N61">
-        <v>336.76746141</v>
+        <v>335.6770794</v>
       </c>
       <c r="O61">
-        <v>99.34640111595</v>
+        <v>99.024738423</v>
       </c>
       <c r="P61">
-        <v>237.42106029405</v>
+        <v>236.652340977</v>
       </c>
       <c r="Q61">
-        <v>239.82106029405</v>
+        <v>239.052340977</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1210743749048066</v>
+        <v>0.1226806596165896</v>
       </c>
       <c r="T61">
-        <v>1.164470639657397</v>
+        <v>1.189319353288926</v>
       </c>
       <c r="U61">
         <v>0.0543</v>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>6.234792047555667</v>
+        <v>6.130878846763072</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.07204116384663586</v>
+        <v>0.07228579898230103</v>
       </c>
       <c r="C62">
-        <v>1001.475243402858</v>
+        <v>976.5882408308091</v>
       </c>
       <c r="D62">
-        <v>2107.817243402858</v>
+        <v>2103.010940830809</v>
       </c>
       <c r="E62">
-        <v>1199.872</v>
+        <v>1219.9527</v>
       </c>
       <c r="F62">
-        <v>1204.842</v>
+        <v>1224.9227</v>
       </c>
       <c r="G62">
         <v>98.5</v>
@@ -6371,45 +6371,45 @@
         <v>401.1</v>
       </c>
       <c r="M62">
-        <v>65.4229206</v>
+        <v>67.73822530999999</v>
       </c>
       <c r="N62">
-        <v>335.6770794</v>
+        <v>333.3617746900001</v>
       </c>
       <c r="O62">
-        <v>99.024738423</v>
+        <v>98.34172353355001</v>
       </c>
       <c r="P62">
-        <v>236.652340977</v>
+        <v>235.0200511564501</v>
       </c>
       <c r="Q62">
-        <v>239.052340977</v>
+        <v>237.4200511564501</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1226806596165896</v>
+        <v>0.1243693179033359</v>
       </c>
       <c r="T62">
-        <v>1.189319353288926</v>
+        <v>1.2154423599272</v>
       </c>
       <c r="U62">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V62">
         <v>0.295</v>
       </c>
       <c r="W62">
-        <v>0.0382815</v>
+        <v>0.03898650000000001</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y62">
-        <v>6.130878846763072</v>
+        <v>5.921324306392581</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.07228579898230103</v>
+        <v>0.07210743411796618</v>
       </c>
       <c r="C63">
-        <v>976.5882408308091</v>
+        <v>960.0096750700059</v>
       </c>
       <c r="D63">
-        <v>2103.010940830809</v>
+        <v>2106.513075070006</v>
       </c>
       <c r="E63">
-        <v>1219.9527</v>
+        <v>1240.0334</v>
       </c>
       <c r="F63">
-        <v>1224.9227</v>
+        <v>1245.0034</v>
       </c>
       <c r="G63">
         <v>98.5</v>
@@ -6453,28 +6453,28 @@
         <v>401.1</v>
       </c>
       <c r="M63">
-        <v>67.73822530999999</v>
+        <v>68.84868802000001</v>
       </c>
       <c r="N63">
-        <v>333.3617746900001</v>
+        <v>332.25131198</v>
       </c>
       <c r="O63">
-        <v>98.34172353355001</v>
+        <v>98.0141370341</v>
       </c>
       <c r="P63">
-        <v>235.0200511564501</v>
+        <v>234.2371749459</v>
       </c>
       <c r="Q63">
-        <v>237.4200511564501</v>
+        <v>236.6371749459</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1243693179033359</v>
+        <v>0.1261468529420162</v>
       </c>
       <c r="T63">
-        <v>1.2154423599272</v>
+        <v>1.2429402616517</v>
       </c>
       <c r="U63">
         <v>0.0553</v>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>5.921324306392581</v>
+        <v>5.825819075644311</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.07210743411796618</v>
+        <v>0.07192906925363134</v>
       </c>
       <c r="C64">
-        <v>960.0096750700059</v>
+        <v>943.4427929412886</v>
       </c>
       <c r="D64">
-        <v>2106.513075070006</v>
+        <v>2110.026892941289</v>
       </c>
       <c r="E64">
-        <v>1240.0334</v>
+        <v>1260.1141</v>
       </c>
       <c r="F64">
-        <v>1245.0034</v>
+        <v>1265.0841</v>
       </c>
       <c r="G64">
         <v>98.5</v>
@@ -6535,28 +6535,28 @@
         <v>401.1</v>
       </c>
       <c r="M64">
-        <v>68.84868802000001</v>
+        <v>69.95915073</v>
       </c>
       <c r="N64">
-        <v>332.25131198</v>
+        <v>331.14084927</v>
       </c>
       <c r="O64">
-        <v>98.0141370341</v>
+        <v>97.68655053465</v>
       </c>
       <c r="P64">
-        <v>234.2371749459</v>
+        <v>233.45429873535</v>
       </c>
       <c r="Q64">
-        <v>236.6371749459</v>
+        <v>235.85429873535</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1261468529420162</v>
+        <v>0.1280204709557604</v>
       </c>
       <c r="T64">
-        <v>1.2429402616517</v>
+        <v>1.271924536442388</v>
       </c>
       <c r="U64">
         <v>0.0553</v>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>5.825819075644311</v>
+        <v>5.73334575698329</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.07192906925363134</v>
+        <v>0.0717507043892965</v>
       </c>
       <c r="C65">
-        <v>943.4427929412886</v>
+        <v>926.8876530098073</v>
       </c>
       <c r="D65">
-        <v>2110.026892941289</v>
+        <v>2113.552453009807</v>
       </c>
       <c r="E65">
-        <v>1260.1141</v>
+        <v>1280.1948</v>
       </c>
       <c r="F65">
-        <v>1265.0841</v>
+        <v>1285.1648</v>
       </c>
       <c r="G65">
         <v>98.5</v>
@@ -6617,28 +6617,28 @@
         <v>401.1</v>
       </c>
       <c r="M65">
-        <v>69.95915073</v>
+        <v>71.06961344</v>
       </c>
       <c r="N65">
-        <v>331.14084927</v>
+        <v>330.03038656</v>
       </c>
       <c r="O65">
-        <v>97.68655053465</v>
+        <v>97.3589640352</v>
       </c>
       <c r="P65">
-        <v>233.45429873535</v>
+        <v>232.6714225248</v>
       </c>
       <c r="Q65">
-        <v>235.85429873535</v>
+        <v>235.0714225248</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1280204709557604</v>
+        <v>0.1299981788591569</v>
       </c>
       <c r="T65">
-        <v>1.271924536442388</v>
+        <v>1.302519048721449</v>
       </c>
       <c r="U65">
         <v>0.0553</v>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>5.73334575698329</v>
+        <v>5.643762229530427</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.0717507043892965</v>
+        <v>0.07157233952496164</v>
       </c>
       <c r="C66">
-        <v>926.8876530098073</v>
+        <v>910.3443142327837</v>
       </c>
       <c r="D66">
-        <v>2113.552453009807</v>
+        <v>2117.089814232784</v>
       </c>
       <c r="E66">
-        <v>1280.1948</v>
+        <v>1300.2755</v>
       </c>
       <c r="F66">
-        <v>1285.1648</v>
+        <v>1305.2455</v>
       </c>
       <c r="G66">
         <v>98.5</v>
@@ -6699,28 +6699,28 @@
         <v>401.1</v>
       </c>
       <c r="M66">
-        <v>71.06961344</v>
+        <v>72.18007615</v>
       </c>
       <c r="N66">
-        <v>330.03038656</v>
+        <v>328.91992385</v>
       </c>
       <c r="O66">
-        <v>97.3589640352</v>
+        <v>97.03137753575001</v>
       </c>
       <c r="P66">
-        <v>232.6714225248</v>
+        <v>231.88854631425</v>
       </c>
       <c r="Q66">
-        <v>235.0714225248</v>
+        <v>234.28854631425</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1299981788591569</v>
+        <v>0.1320888986427476</v>
       </c>
       <c r="T66">
-        <v>1.302519048721449</v>
+        <v>1.334861818845026</v>
       </c>
       <c r="U66">
         <v>0.0553</v>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>5.643762229530427</v>
+        <v>5.556935118306882</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.07157233952496164</v>
+        <v>0.0713939746606268</v>
       </c>
       <c r="C67">
-        <v>910.3443142327837</v>
+        <v>893.8128359627967</v>
       </c>
       <c r="D67">
-        <v>2117.089814232784</v>
+        <v>2120.639035962797</v>
       </c>
       <c r="E67">
-        <v>1300.2755</v>
+        <v>1320.3562</v>
       </c>
       <c r="F67">
-        <v>1305.2455</v>
+        <v>1325.3262</v>
       </c>
       <c r="G67">
         <v>98.5</v>
@@ -6781,28 +6781,28 @@
         <v>401.1</v>
       </c>
       <c r="M67">
-        <v>72.18007615</v>
+        <v>73.29053886</v>
       </c>
       <c r="N67">
-        <v>328.91992385</v>
+        <v>327.8094611400001</v>
       </c>
       <c r="O67">
-        <v>97.03137753575001</v>
+        <v>96.7037910363</v>
       </c>
       <c r="P67">
-        <v>231.88854631425</v>
+        <v>231.1056701037</v>
       </c>
       <c r="Q67">
-        <v>234.28854631425</v>
+        <v>233.5056701037001</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1320888986427476</v>
+        <v>0.13430260194302</v>
       </c>
       <c r="T67">
-        <v>1.334861818845026</v>
+        <v>1.369107104858226</v>
       </c>
       <c r="U67">
         <v>0.0553</v>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>5.556935118306882</v>
+        <v>5.472739131665869</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.0713939746606268</v>
+        <v>0.07121560979629196</v>
       </c>
       <c r="C68">
-        <v>893.8128359627967</v>
+        <v>877.2932779511034</v>
       </c>
       <c r="D68">
-        <v>2120.639035962797</v>
+        <v>2124.200177951103</v>
       </c>
       <c r="E68">
-        <v>1320.3562</v>
+        <v>1340.4369</v>
       </c>
       <c r="F68">
-        <v>1325.3262</v>
+        <v>1345.4069</v>
       </c>
       <c r="G68">
         <v>98.5</v>
@@ -6863,28 +6863,28 @@
         <v>401.1</v>
       </c>
       <c r="M68">
-        <v>73.29053886</v>
+        <v>74.40100157000001</v>
       </c>
       <c r="N68">
-        <v>327.8094611400001</v>
+        <v>326.69899843</v>
       </c>
       <c r="O68">
-        <v>96.7037910363</v>
+        <v>96.37620453685</v>
       </c>
       <c r="P68">
-        <v>231.1056701037</v>
+        <v>230.32279389315</v>
       </c>
       <c r="Q68">
-        <v>233.5056701037001</v>
+        <v>232.72279389315</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.13430260194302</v>
+        <v>0.1366504690796726</v>
       </c>
       <c r="T68">
-        <v>1.369107104858226</v>
+        <v>1.405427862751014</v>
       </c>
       <c r="U68">
         <v>0.0553</v>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>5.472739131665869</v>
+        <v>5.391056458058915</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.07121560979629196</v>
+        <v>0.07103724493195712</v>
       </c>
       <c r="C69">
-        <v>877.2932779511034</v>
+        <v>860.7857003509928</v>
       </c>
       <c r="D69">
-        <v>2124.200177951103</v>
+        <v>2127.773300350993</v>
       </c>
       <c r="E69">
-        <v>1340.4369</v>
+        <v>1360.5176</v>
       </c>
       <c r="F69">
-        <v>1345.4069</v>
+        <v>1365.4876</v>
       </c>
       <c r="G69">
         <v>98.5</v>
@@ -6945,28 +6945,28 @@
         <v>401.1</v>
       </c>
       <c r="M69">
-        <v>74.40100157000001</v>
+        <v>75.51146428000001</v>
       </c>
       <c r="N69">
-        <v>326.69899843</v>
+        <v>325.58853572</v>
       </c>
       <c r="O69">
-        <v>96.37620453685</v>
+        <v>96.04861803739999</v>
       </c>
       <c r="P69">
-        <v>230.32279389315</v>
+        <v>229.5399176826</v>
       </c>
       <c r="Q69">
-        <v>232.72279389315</v>
+        <v>231.9399176826</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1366504690796726</v>
+        <v>0.139145077912366</v>
       </c>
       <c r="T69">
-        <v>1.405427862751014</v>
+        <v>1.444018668012101</v>
       </c>
       <c r="U69">
         <v>0.0553</v>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>5.391056458058915</v>
+        <v>5.311776216028636</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.07103724493195712</v>
+        <v>0.07085888006762228</v>
       </c>
       <c r="C70">
-        <v>860.7857003509928</v>
+        <v>844.2901637211705</v>
       </c>
       <c r="D70">
-        <v>2127.773300350993</v>
+        <v>2131.358463721171</v>
       </c>
       <c r="E70">
-        <v>1360.5176</v>
+        <v>1380.5983</v>
       </c>
       <c r="F70">
-        <v>1365.4876</v>
+        <v>1385.5683</v>
       </c>
       <c r="G70">
         <v>98.5</v>
@@ -7027,28 +7027,28 @@
         <v>401.1</v>
       </c>
       <c r="M70">
-        <v>75.51146428000001</v>
+        <v>76.62192699000001</v>
       </c>
       <c r="N70">
-        <v>325.58853572</v>
+        <v>324.47807301</v>
       </c>
       <c r="O70">
-        <v>96.04861803739999</v>
+        <v>95.72103153795</v>
       </c>
       <c r="P70">
-        <v>229.5399176826</v>
+        <v>228.75704147205</v>
       </c>
       <c r="Q70">
-        <v>231.9399176826</v>
+        <v>231.15704147205</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.139145077912366</v>
+        <v>0.1418006292503944</v>
       </c>
       <c r="T70">
-        <v>1.444018668012101</v>
+        <v>1.485099202644872</v>
       </c>
       <c r="U70">
         <v>0.0553</v>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>5.311776216028636</v>
+        <v>5.234793952028222</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.07085888006762228</v>
+        <v>0.07068051520328743</v>
       </c>
       <c r="C71">
-        <v>844.2901637211705</v>
+        <v>827.8067290291826</v>
       </c>
       <c r="D71">
-        <v>2131.358463721171</v>
+        <v>2134.955729029183</v>
       </c>
       <c r="E71">
-        <v>1380.5983</v>
+        <v>1400.679</v>
       </c>
       <c r="F71">
-        <v>1385.5683</v>
+        <v>1405.649</v>
       </c>
       <c r="G71">
         <v>98.5</v>
@@ -7109,28 +7109,28 @@
         <v>401.1</v>
       </c>
       <c r="M71">
-        <v>76.62192699000001</v>
+        <v>77.73238970000001</v>
       </c>
       <c r="N71">
-        <v>324.47807301</v>
+        <v>323.3676103</v>
       </c>
       <c r="O71">
-        <v>95.72103153795</v>
+        <v>95.3934450385</v>
       </c>
       <c r="P71">
-        <v>228.75704147205</v>
+        <v>227.9741652615</v>
       </c>
       <c r="Q71">
-        <v>231.15704147205</v>
+        <v>230.3741652615</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1418006292503944</v>
+        <v>0.1446332173442914</v>
       </c>
       <c r="T71">
-        <v>1.485099202644872</v>
+        <v>1.528918439586493</v>
       </c>
       <c r="U71">
         <v>0.0553</v>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>5.234793952028222</v>
+        <v>5.160011181284961</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.07068051520328743</v>
+        <v>0.0705021503389526</v>
       </c>
       <c r="C72">
-        <v>827.8067290291826</v>
+        <v>811.3354576548693</v>
       </c>
       <c r="D72">
-        <v>2134.955729029183</v>
+        <v>2138.565157654869</v>
       </c>
       <c r="E72">
-        <v>1400.679</v>
+        <v>1420.7597</v>
       </c>
       <c r="F72">
-        <v>1405.649</v>
+        <v>1425.7297</v>
       </c>
       <c r="G72">
         <v>98.5</v>
@@ -7191,28 +7191,28 @@
         <v>401.1</v>
       </c>
       <c r="M72">
-        <v>77.73238970000001</v>
+        <v>78.84285241000001</v>
       </c>
       <c r="N72">
-        <v>323.3676103</v>
+        <v>322.25714759</v>
       </c>
       <c r="O72">
-        <v>95.3934450385</v>
+        <v>95.06585853905001</v>
       </c>
       <c r="P72">
-        <v>227.9741652615</v>
+        <v>227.19128905095</v>
       </c>
       <c r="Q72">
-        <v>230.3741652615</v>
+        <v>229.5912890509501</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1446332173442914</v>
+        <v>0.1476611563412158</v>
       </c>
       <c r="T72">
-        <v>1.528918439586493</v>
+        <v>1.575759692868917</v>
       </c>
       <c r="U72">
         <v>0.0553</v>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>5.160011181284961</v>
+        <v>5.087334967464047</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.0705021503389526</v>
+        <v>0.07032378547461776</v>
       </c>
       <c r="C73">
-        <v>811.3354576548695</v>
+        <v>794.8764113938578</v>
       </c>
       <c r="D73">
-        <v>2138.565157654869</v>
+        <v>2142.186811393858</v>
       </c>
       <c r="E73">
-        <v>1420.7597</v>
+        <v>1440.8404</v>
       </c>
       <c r="F73">
-        <v>1425.7297</v>
+        <v>1445.8104</v>
       </c>
       <c r="G73">
         <v>98.5</v>
@@ -7273,28 +7273,28 @@
         <v>401.1</v>
       </c>
       <c r="M73">
-        <v>78.84285240999999</v>
+        <v>79.95331512</v>
       </c>
       <c r="N73">
-        <v>322.25714759</v>
+        <v>321.14668488</v>
       </c>
       <c r="O73">
-        <v>95.06585853905001</v>
+        <v>94.73827203959999</v>
       </c>
       <c r="P73">
-        <v>227.19128905095</v>
+        <v>226.4084128404</v>
       </c>
       <c r="Q73">
-        <v>229.5912890509501</v>
+        <v>228.8084128404</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1476611563412158</v>
+        <v>0.1509053766950634</v>
       </c>
       <c r="T73">
-        <v>1.575759692868916</v>
+        <v>1.625946749957226</v>
       </c>
       <c r="U73">
         <v>0.0553</v>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>5.087334967464048</v>
+        <v>5.01667753736038</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.07032378547461776</v>
+        <v>0.07014542061028291</v>
       </c>
       <c r="C74">
-        <v>794.8764113938578</v>
+        <v>778.4296524610886</v>
       </c>
       <c r="D74">
-        <v>2142.186811393858</v>
+        <v>2145.820752461088</v>
       </c>
       <c r="E74">
-        <v>1440.8404</v>
+        <v>1460.9211</v>
       </c>
       <c r="F74">
-        <v>1445.8104</v>
+        <v>1465.8911</v>
       </c>
       <c r="G74">
         <v>98.5</v>
@@ -7355,28 +7355,28 @@
         <v>401.1</v>
       </c>
       <c r="M74">
-        <v>79.95331512</v>
+        <v>81.06377782999999</v>
       </c>
       <c r="N74">
-        <v>321.14668488</v>
+        <v>320.03622217</v>
       </c>
       <c r="O74">
-        <v>94.73827203959999</v>
+        <v>94.41068554015</v>
       </c>
       <c r="P74">
-        <v>226.4084128404</v>
+        <v>225.62553662985</v>
       </c>
       <c r="Q74">
-        <v>228.8084128404</v>
+        <v>228.0255366298501</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1509053766950634</v>
+        <v>0.1543899096677144</v>
       </c>
       <c r="T74">
-        <v>1.625946749957226</v>
+        <v>1.679851366829856</v>
       </c>
       <c r="U74">
         <v>0.0553</v>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>5.01667753736038</v>
+        <v>4.947955927259553</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.07014542061028291</v>
+        <v>0.06996705574594807</v>
       </c>
       <c r="C75">
-        <v>778.4296524610886</v>
+        <v>761.9952434943764</v>
       </c>
       <c r="D75">
-        <v>2145.820752461088</v>
+        <v>2149.467043494376</v>
       </c>
       <c r="E75">
-        <v>1460.9211</v>
+        <v>1481.0018</v>
       </c>
       <c r="F75">
-        <v>1465.8911</v>
+        <v>1485.9718</v>
       </c>
       <c r="G75">
         <v>98.5</v>
@@ -7437,28 +7437,28 @@
         <v>401.1</v>
       </c>
       <c r="M75">
-        <v>81.06377782999999</v>
+        <v>82.17424054</v>
       </c>
       <c r="N75">
-        <v>320.03622217</v>
+        <v>318.92575946</v>
       </c>
       <c r="O75">
-        <v>94.41068554015</v>
+        <v>94.08309904069999</v>
       </c>
       <c r="P75">
-        <v>225.62553662985</v>
+        <v>224.8426604193</v>
       </c>
       <c r="Q75">
-        <v>228.0255366298501</v>
+        <v>227.2426604193</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1543899096677144</v>
+        <v>0.1581424836382617</v>
       </c>
       <c r="T75">
-        <v>1.679851366829856</v>
+        <v>1.737902492692688</v>
       </c>
       <c r="U75">
         <v>0.0553</v>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>4.947955927259553</v>
+        <v>4.881091657972261</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.06996705574594807</v>
+        <v>0.06978869088161321</v>
       </c>
       <c r="C76">
-        <v>761.9952434943764</v>
+        <v>745.5732475580114</v>
       </c>
       <c r="D76">
-        <v>2149.467043494376</v>
+        <v>2153.125747558011</v>
       </c>
       <c r="E76">
-        <v>1481.0018</v>
+        <v>1501.0825</v>
       </c>
       <c r="F76">
-        <v>1485.9718</v>
+        <v>1506.0525</v>
       </c>
       <c r="G76">
         <v>98.5</v>
@@ -7519,28 +7519,28 @@
         <v>401.1</v>
       </c>
       <c r="M76">
-        <v>82.17424054</v>
+        <v>83.28470325000001</v>
       </c>
       <c r="N76">
-        <v>318.92575946</v>
+        <v>317.81529675</v>
       </c>
       <c r="O76">
-        <v>94.08309904069999</v>
+        <v>93.75551254125</v>
       </c>
       <c r="P76">
-        <v>224.8426604193</v>
+        <v>224.05978420875</v>
       </c>
       <c r="Q76">
-        <v>227.2426604193</v>
+        <v>226.45978420875</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1581424836382617</v>
+        <v>0.1621952635264529</v>
       </c>
       <c r="T76">
-        <v>1.737902492692688</v>
+        <v>1.800597708624547</v>
       </c>
       <c r="U76">
         <v>0.0553</v>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>4.881091657972261</v>
+        <v>4.816010435865964</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.06978869088161321</v>
+        <v>0.06961032601727839</v>
       </c>
       <c r="C77">
-        <v>745.5732475580114</v>
+        <v>729.1637281463939</v>
       </c>
       <c r="D77">
-        <v>2153.125747558011</v>
+        <v>2156.796928146394</v>
       </c>
       <c r="E77">
-        <v>1501.0825</v>
+        <v>1521.1632</v>
       </c>
       <c r="F77">
-        <v>1506.0525</v>
+        <v>1526.1332</v>
       </c>
       <c r="G77">
         <v>98.5</v>
@@ -7601,28 +7601,28 @@
         <v>401.1</v>
       </c>
       <c r="M77">
-        <v>83.28470325000001</v>
+        <v>84.39516596</v>
       </c>
       <c r="N77">
-        <v>317.81529675</v>
+        <v>316.70483404</v>
       </c>
       <c r="O77">
-        <v>93.75551254125</v>
+        <v>93.42792604180001</v>
       </c>
       <c r="P77">
-        <v>224.05978420875</v>
+        <v>223.2769079982</v>
       </c>
       <c r="Q77">
-        <v>226.45978420875</v>
+        <v>225.6769079982001</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1621952635264529</v>
+        <v>0.1665857750719932</v>
       </c>
       <c r="T77">
-        <v>1.800597708624547</v>
+        <v>1.86851752588406</v>
       </c>
       <c r="U77">
         <v>0.0553</v>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>4.816010435865964</v>
+        <v>4.752641877499308</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.06961032601727839</v>
+        <v>0.06943196115294353</v>
       </c>
       <c r="C78">
-        <v>729.1637281463939</v>
+        <v>712.766749187708</v>
       </c>
       <c r="D78">
-        <v>2156.796928146394</v>
+        <v>2160.480649187708</v>
       </c>
       <c r="E78">
-        <v>1521.1632</v>
+        <v>1541.2439</v>
       </c>
       <c r="F78">
-        <v>1526.1332</v>
+        <v>1546.2139</v>
       </c>
       <c r="G78">
         <v>98.5</v>
@@ -7683,28 +7683,28 @@
         <v>401.1</v>
       </c>
       <c r="M78">
-        <v>84.39516596</v>
+        <v>85.50562867000001</v>
       </c>
       <c r="N78">
-        <v>316.70483404</v>
+        <v>315.59437133</v>
       </c>
       <c r="O78">
-        <v>93.42792604180001</v>
+        <v>93.10033954235</v>
       </c>
       <c r="P78">
-        <v>223.2769079982</v>
+        <v>222.49403178765</v>
       </c>
       <c r="Q78">
-        <v>225.6769079982001</v>
+        <v>224.89403178765</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1665857750719932</v>
+        <v>0.1713580702301893</v>
       </c>
       <c r="T78">
-        <v>1.86851752588406</v>
+        <v>1.942343414209618</v>
       </c>
       <c r="U78">
         <v>0.0553</v>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>4.752641877499308</v>
+        <v>4.690919255713601</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.06943196115294353</v>
+        <v>0.06925359628860869</v>
       </c>
       <c r="C79">
-        <v>712.766749187708</v>
+        <v>696.3823750476306</v>
       </c>
       <c r="D79">
-        <v>2160.480649187708</v>
+        <v>2164.176975047631</v>
       </c>
       <c r="E79">
-        <v>1541.2439</v>
+        <v>1561.3246</v>
       </c>
       <c r="F79">
-        <v>1546.2139</v>
+        <v>1566.2946</v>
       </c>
       <c r="G79">
         <v>98.5</v>
@@ -7765,28 +7765,28 @@
         <v>401.1</v>
       </c>
       <c r="M79">
-        <v>85.50562867000001</v>
+        <v>86.61609138</v>
       </c>
       <c r="N79">
-        <v>315.59437133</v>
+        <v>314.48390862</v>
       </c>
       <c r="O79">
-        <v>93.10033954235</v>
+        <v>92.77275304290001</v>
       </c>
       <c r="P79">
-        <v>222.49403178765</v>
+        <v>221.7111555771</v>
       </c>
       <c r="Q79">
-        <v>224.89403178765</v>
+        <v>224.1111555771</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1713580702301893</v>
+        <v>0.1765642104027668</v>
       </c>
       <c r="T79">
-        <v>1.942343414209618</v>
+        <v>2.022880746928409</v>
       </c>
       <c r="U79">
         <v>0.0553</v>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>4.690919255713601</v>
+        <v>4.630779265255735</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.06925359628860869</v>
+        <v>0.06907523142427384</v>
       </c>
       <c r="C80">
-        <v>696.3823750476306</v>
+        <v>680.0106705330838</v>
       </c>
       <c r="D80">
-        <v>2164.176975047631</v>
+        <v>2167.885970533084</v>
       </c>
       <c r="E80">
-        <v>1561.3246</v>
+        <v>1581.4053</v>
       </c>
       <c r="F80">
-        <v>1566.2946</v>
+        <v>1586.3753</v>
       </c>
       <c r="G80">
         <v>98.5</v>
@@ -7847,28 +7847,28 @@
         <v>401.1</v>
       </c>
       <c r="M80">
-        <v>86.61609138</v>
+        <v>87.72655408999999</v>
       </c>
       <c r="N80">
-        <v>314.48390862</v>
+        <v>313.37344591</v>
       </c>
       <c r="O80">
-        <v>92.77275304290001</v>
+        <v>92.44516654345001</v>
       </c>
       <c r="P80">
-        <v>221.7111555771</v>
+        <v>220.92827936655</v>
       </c>
       <c r="Q80">
-        <v>224.1111555771</v>
+        <v>223.32827936655</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1765642104027668</v>
+        <v>0.1822661734489231</v>
       </c>
       <c r="T80">
-        <v>2.022880746928409</v>
+        <v>2.111088301810894</v>
       </c>
       <c r="U80">
         <v>0.0553</v>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>4.630779265255735</v>
+        <v>4.572161806201866</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.06907523142427384</v>
+        <v>0.068896866559939</v>
       </c>
       <c r="C81">
-        <v>680.0106705330838</v>
+        <v>663.6517008960182</v>
       </c>
       <c r="D81">
-        <v>2167.885970533084</v>
+        <v>2171.607700896018</v>
       </c>
       <c r="E81">
-        <v>1581.4053</v>
+        <v>1601.486</v>
       </c>
       <c r="F81">
-        <v>1586.3753</v>
+        <v>1606.456</v>
       </c>
       <c r="G81">
         <v>98.5</v>
@@ -7929,28 +7929,28 @@
         <v>401.1</v>
       </c>
       <c r="M81">
-        <v>87.72655408999999</v>
+        <v>88.83701680000001</v>
       </c>
       <c r="N81">
-        <v>313.37344591</v>
+        <v>312.2629832</v>
       </c>
       <c r="O81">
-        <v>92.44516654345001</v>
+        <v>92.11758004399999</v>
       </c>
       <c r="P81">
-        <v>220.92827936655</v>
+        <v>220.145403156</v>
       </c>
       <c r="Q81">
-        <v>223.32827936655</v>
+        <v>222.545403156</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.1822661734489231</v>
+        <v>0.188538332799695</v>
       </c>
       <c r="T81">
-        <v>2.111088301810894</v>
+        <v>2.208116612181627</v>
       </c>
       <c r="U81">
         <v>0.0553</v>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>4.572161806201866</v>
+        <v>4.515009783624341</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.068896866559939</v>
+        <v>0.07014612669560416</v>
       </c>
       <c r="C82">
-        <v>663.6517008960182</v>
+        <v>617.7696426283883</v>
       </c>
       <c r="D82">
-        <v>2171.607700896018</v>
+        <v>2145.806342628388</v>
       </c>
       <c r="E82">
-        <v>1601.486</v>
+        <v>1621.5667</v>
       </c>
       <c r="F82">
-        <v>1606.456</v>
+        <v>1626.5367</v>
       </c>
       <c r="G82">
         <v>98.5</v>
@@ -8011,45 +8011,45 @@
         <v>401.1</v>
       </c>
       <c r="M82">
-        <v>88.83701680000001</v>
+        <v>94.01382126000001</v>
       </c>
       <c r="N82">
-        <v>312.2629832</v>
+        <v>307.08617874</v>
       </c>
       <c r="O82">
-        <v>92.11758004399999</v>
+        <v>90.59042272830001</v>
       </c>
       <c r="P82">
-        <v>220.145403156</v>
+        <v>216.4957560117</v>
       </c>
       <c r="Q82">
-        <v>222.545403156</v>
+        <v>218.8957560117</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.188538332799695</v>
+        <v>0.1954707194505482</v>
       </c>
       <c r="T82">
-        <v>2.208116612181627</v>
+        <v>2.315358428907174</v>
       </c>
       <c r="U82">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V82">
         <v>0.295</v>
       </c>
       <c r="W82">
-        <v>0.03898650000000001</v>
+        <v>0.04074900000000001</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y82">
-        <v>4.515009783624341</v>
+        <v>4.266393968720169</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.07014612669560416</v>
+        <v>0.06998538683126931</v>
       </c>
       <c r="C83">
-        <v>617.7696426283883</v>
+        <v>600.9743321319497</v>
       </c>
       <c r="D83">
-        <v>2145.806342628388</v>
+        <v>2149.09173213195</v>
       </c>
       <c r="E83">
-        <v>1621.5667</v>
+        <v>1641.6474</v>
       </c>
       <c r="F83">
-        <v>1626.5367</v>
+        <v>1646.6174</v>
       </c>
       <c r="G83">
         <v>98.5</v>
@@ -8093,28 +8093,28 @@
         <v>401.1</v>
       </c>
       <c r="M83">
-        <v>94.01382126000001</v>
+        <v>95.17448572000001</v>
       </c>
       <c r="N83">
-        <v>307.08617874</v>
+        <v>305.92551428</v>
       </c>
       <c r="O83">
-        <v>90.59042272830001</v>
+        <v>90.24802671259999</v>
       </c>
       <c r="P83">
-        <v>216.4957560117</v>
+        <v>215.6774875674</v>
       </c>
       <c r="Q83">
-        <v>218.8957560117</v>
+        <v>218.0774875674</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.1954707194505482</v>
+        <v>0.2031733712848296</v>
       </c>
       <c r="T83">
-        <v>2.315358428907174</v>
+        <v>2.434516003046672</v>
       </c>
       <c r="U83">
         <v>0.0578</v>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>4.266393968720169</v>
+        <v>4.214364773979679</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.06998538683126931</v>
+        <v>0.06982464696693447</v>
       </c>
       <c r="C84">
-        <v>600.9743321319497</v>
+        <v>584.1890974148623</v>
       </c>
       <c r="D84">
-        <v>2149.09173213195</v>
+        <v>2152.387197414862</v>
       </c>
       <c r="E84">
-        <v>1641.6474</v>
+        <v>1661.7281</v>
       </c>
       <c r="F84">
-        <v>1646.6174</v>
+        <v>1666.6981</v>
       </c>
       <c r="G84">
         <v>98.5</v>
@@ -8175,28 +8175,28 @@
         <v>401.1</v>
       </c>
       <c r="M84">
-        <v>95.17448572000001</v>
+        <v>96.33515018000001</v>
       </c>
       <c r="N84">
-        <v>305.92551428</v>
+        <v>304.76484982</v>
       </c>
       <c r="O84">
-        <v>90.24802671259999</v>
+        <v>89.90563069689999</v>
       </c>
       <c r="P84">
-        <v>215.6774875674</v>
+        <v>214.8592191231</v>
       </c>
       <c r="Q84">
-        <v>218.0774875674</v>
+        <v>217.2592191231</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2031733712848296</v>
+        <v>0.2117822174525558</v>
       </c>
       <c r="T84">
-        <v>2.434516003046672</v>
+        <v>2.567692115320228</v>
       </c>
       <c r="U84">
         <v>0.0578</v>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>4.214364773979679</v>
+        <v>4.163589294775104</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.06982464696693447</v>
+        <v>0.06966390710259965</v>
       </c>
       <c r="C85">
-        <v>584.1890974148623</v>
+        <v>567.4139848995878</v>
       </c>
       <c r="D85">
-        <v>2152.387197414862</v>
+        <v>2155.692784899588</v>
       </c>
       <c r="E85">
-        <v>1661.7281</v>
+        <v>1681.8088</v>
       </c>
       <c r="F85">
-        <v>1666.6981</v>
+        <v>1686.7788</v>
       </c>
       <c r="G85">
         <v>98.5</v>
@@ -8257,28 +8257,28 @@
         <v>401.1</v>
       </c>
       <c r="M85">
-        <v>96.33515018000001</v>
+        <v>97.49581464000001</v>
       </c>
       <c r="N85">
-        <v>304.76484982</v>
+        <v>303.60418536</v>
       </c>
       <c r="O85">
-        <v>89.90563069689999</v>
+        <v>89.5632346812</v>
       </c>
       <c r="P85">
-        <v>214.8592191231</v>
+        <v>214.0409506788</v>
       </c>
       <c r="Q85">
-        <v>217.2592191231</v>
+        <v>216.4409506788</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2117822174525558</v>
+        <v>0.2214671693912478</v>
       </c>
       <c r="T85">
-        <v>2.567692115320228</v>
+        <v>2.717515241627979</v>
       </c>
       <c r="U85">
         <v>0.0578</v>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>4.163589294775104</v>
+        <v>4.114022755551591</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.06966390710259963</v>
+        <v>0.0695031672382648</v>
       </c>
       <c r="C86">
-        <v>567.4139848995881</v>
+        <v>550.6490412942037</v>
       </c>
       <c r="D86">
-        <v>2155.692784899588</v>
+        <v>2159.008541294203</v>
       </c>
       <c r="E86">
-        <v>1681.8088</v>
+        <v>1701.8895</v>
       </c>
       <c r="F86">
-        <v>1686.7788</v>
+        <v>1706.8595</v>
       </c>
       <c r="G86">
         <v>98.5</v>
@@ -8339,28 +8339,28 @@
         <v>401.1</v>
       </c>
       <c r="M86">
-        <v>97.49581463999999</v>
+        <v>98.6564791</v>
       </c>
       <c r="N86">
-        <v>303.60418536</v>
+        <v>302.4435209</v>
       </c>
       <c r="O86">
-        <v>89.5632346812</v>
+        <v>89.2208386655</v>
       </c>
       <c r="P86">
-        <v>214.0409506788</v>
+        <v>213.2226822345</v>
       </c>
       <c r="Q86">
-        <v>216.4409506788</v>
+        <v>215.6226822345</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2214671693912477</v>
+        <v>0.2324434482550986</v>
       </c>
       <c r="T86">
-        <v>2.717515241627977</v>
+        <v>2.887314784776761</v>
       </c>
       <c r="U86">
         <v>0.0578</v>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>4.114022755551592</v>
+        <v>4.06562248783922</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.0695031672382648</v>
+        <v>0.06934242737392995</v>
       </c>
       <c r="C87">
-        <v>550.6490412942037</v>
+        <v>533.8943135946042</v>
       </c>
       <c r="D87">
-        <v>2159.008541294203</v>
+        <v>2162.334513594604</v>
       </c>
       <c r="E87">
-        <v>1701.8895</v>
+        <v>1721.9702</v>
       </c>
       <c r="F87">
-        <v>1706.8595</v>
+        <v>1726.9402</v>
       </c>
       <c r="G87">
         <v>98.5</v>
@@ -8421,28 +8421,28 @@
         <v>401.1</v>
       </c>
       <c r="M87">
-        <v>98.6564791</v>
+        <v>99.81714356000001</v>
       </c>
       <c r="N87">
-        <v>302.4435209</v>
+        <v>301.28285644</v>
       </c>
       <c r="O87">
-        <v>89.2208386655</v>
+        <v>88.87844264980001</v>
       </c>
       <c r="P87">
-        <v>213.2226822345</v>
+        <v>212.4044137902</v>
       </c>
       <c r="Q87">
-        <v>215.6226822345</v>
+        <v>214.8044137902</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2324434482550986</v>
+        <v>0.2449877669566424</v>
       </c>
       <c r="T87">
-        <v>2.887314784776761</v>
+        <v>3.081371405518227</v>
       </c>
       <c r="U87">
         <v>0.0578</v>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>4.06562248783922</v>
+        <v>4.018347807748066</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.06934242737392995</v>
+        <v>0.07132841250959511</v>
       </c>
       <c r="C88">
-        <v>533.8943135946042</v>
+        <v>473.4257277715474</v>
       </c>
       <c r="D88">
-        <v>2162.334513594604</v>
+        <v>2121.946627771547</v>
       </c>
       <c r="E88">
-        <v>1721.9702</v>
+        <v>1742.0509</v>
       </c>
       <c r="F88">
-        <v>1726.9402</v>
+        <v>1747.0209</v>
       </c>
       <c r="G88">
         <v>98.5</v>
@@ -8503,45 +8503,45 @@
         <v>401.1</v>
       </c>
       <c r="M88">
-        <v>99.81714356000001</v>
+        <v>107.09238117</v>
       </c>
       <c r="N88">
-        <v>301.28285644</v>
+        <v>294.00761883</v>
       </c>
       <c r="O88">
-        <v>88.87844264980001</v>
+        <v>86.73224755485001</v>
       </c>
       <c r="P88">
-        <v>212.4044137902</v>
+        <v>207.27537127515</v>
       </c>
       <c r="Q88">
-        <v>214.8044137902</v>
+        <v>209.67537127515</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2449877669566424</v>
+        <v>0.2594619808430392</v>
       </c>
       <c r="T88">
-        <v>3.081371405518227</v>
+        <v>3.305282890989151</v>
       </c>
       <c r="U88">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V88">
         <v>0.295</v>
       </c>
       <c r="W88">
-        <v>0.04074900000000001</v>
+        <v>0.0432165</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y88">
-        <v>4.018347807748066</v>
+        <v>3.745364475212182</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.07132841250959511</v>
+        <v>0.07119234764526026</v>
       </c>
       <c r="C89">
-        <v>473.4257277715474</v>
+        <v>456.0639000386209</v>
       </c>
       <c r="D89">
-        <v>2121.946627771547</v>
+        <v>2124.665500038621</v>
       </c>
       <c r="E89">
-        <v>1742.0509</v>
+        <v>1762.1316</v>
       </c>
       <c r="F89">
-        <v>1747.0209</v>
+        <v>1767.1016</v>
       </c>
       <c r="G89">
         <v>98.5</v>
@@ -8585,28 +8585,28 @@
         <v>401.1</v>
       </c>
       <c r="M89">
-        <v>107.09238117</v>
+        <v>108.32332808</v>
       </c>
       <c r="N89">
-        <v>294.00761883</v>
+        <v>292.77667192</v>
       </c>
       <c r="O89">
-        <v>86.73224755485001</v>
+        <v>86.3691182164</v>
       </c>
       <c r="P89">
-        <v>207.27537127515</v>
+        <v>206.4075537036</v>
       </c>
       <c r="Q89">
-        <v>209.67537127515</v>
+        <v>208.8075537036</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.2594619808430392</v>
+        <v>0.2763485637105021</v>
       </c>
       <c r="T89">
-        <v>3.305282890989151</v>
+        <v>3.566512957371895</v>
       </c>
       <c r="U89">
         <v>0.0613</v>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>3.745364475212182</v>
+        <v>3.702803515266589</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.07119234764526026</v>
+        <v>0.07105628278092541</v>
       </c>
       <c r="C90">
-        <v>456.0639000386209</v>
+        <v>438.7090486831844</v>
       </c>
       <c r="D90">
-        <v>2124.665500038621</v>
+        <v>2127.391348683184</v>
       </c>
       <c r="E90">
-        <v>1762.1316</v>
+        <v>1782.2123</v>
       </c>
       <c r="F90">
-        <v>1767.1016</v>
+        <v>1787.1823</v>
       </c>
       <c r="G90">
         <v>98.5</v>
@@ -8667,28 +8667,28 @@
         <v>401.1</v>
       </c>
       <c r="M90">
-        <v>108.32332808</v>
+        <v>109.55427499</v>
       </c>
       <c r="N90">
-        <v>292.77667192</v>
+        <v>291.54572501</v>
       </c>
       <c r="O90">
-        <v>86.3691182164</v>
+        <v>86.00598887795</v>
       </c>
       <c r="P90">
-        <v>206.4075537036</v>
+        <v>205.53973613205</v>
       </c>
       <c r="Q90">
-        <v>208.8075537036</v>
+        <v>207.93973613205</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.2763485637105021</v>
+        <v>0.2963054343720492</v>
       </c>
       <c r="T90">
-        <v>3.566512957371895</v>
+        <v>3.875239399460592</v>
       </c>
       <c r="U90">
         <v>0.0613</v>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>3.702803515266589</v>
+        <v>3.661198981387189</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.07105628278092541</v>
+        <v>0.07092021791659057</v>
       </c>
       <c r="C91">
-        <v>438.7090486831844</v>
+        <v>421.3612005908503</v>
       </c>
       <c r="D91">
-        <v>2127.391348683184</v>
+        <v>2130.12420059085</v>
       </c>
       <c r="E91">
-        <v>1782.2123</v>
+        <v>1802.293</v>
       </c>
       <c r="F91">
-        <v>1787.1823</v>
+        <v>1807.263</v>
       </c>
       <c r="G91">
         <v>98.5</v>
@@ -8749,28 +8749,28 @@
         <v>401.1</v>
       </c>
       <c r="M91">
-        <v>109.55427499</v>
+        <v>110.7852219</v>
       </c>
       <c r="N91">
-        <v>291.54572501</v>
+        <v>290.3147781</v>
       </c>
       <c r="O91">
-        <v>86.00598887795</v>
+        <v>85.64285953949999</v>
       </c>
       <c r="P91">
-        <v>205.53973613205</v>
+        <v>204.6719185605</v>
       </c>
       <c r="Q91">
-        <v>207.93973613205</v>
+        <v>207.0719185605</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.2963054343720492</v>
+        <v>0.3202536791659057</v>
       </c>
       <c r="T91">
-        <v>3.875239399460592</v>
+        <v>4.245711129967029</v>
       </c>
       <c r="U91">
         <v>0.0613</v>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>3.661198981387189</v>
+        <v>3.620518992705109</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.07092021791659057</v>
+        <v>0.07078415305225574</v>
       </c>
       <c r="C92">
-        <v>421.3612005908503</v>
+        <v>404.0203827855576</v>
       </c>
       <c r="D92">
-        <v>2130.12420059085</v>
+        <v>2132.864082785557</v>
       </c>
       <c r="E92">
-        <v>1802.293</v>
+        <v>1822.3737</v>
       </c>
       <c r="F92">
-        <v>1807.263</v>
+        <v>1827.3437</v>
       </c>
       <c r="G92">
         <v>98.5</v>
@@ -8831,28 +8831,28 @@
         <v>401.1</v>
       </c>
       <c r="M92">
-        <v>110.7852219</v>
+        <v>112.01616881</v>
       </c>
       <c r="N92">
-        <v>290.3147781</v>
+        <v>289.08383119</v>
       </c>
       <c r="O92">
-        <v>85.64285953949999</v>
+        <v>85.27973020105</v>
       </c>
       <c r="P92">
-        <v>204.6719185605</v>
+        <v>203.80410098895</v>
       </c>
       <c r="Q92">
-        <v>207.0719185605</v>
+        <v>206.20410098895</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.3202536791659057</v>
+        <v>0.3495237561361749</v>
       </c>
       <c r="T92">
-        <v>4.245711129967029</v>
+        <v>4.69850991169712</v>
       </c>
       <c r="U92">
         <v>0.0613</v>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>3.620518992705109</v>
+        <v>3.58073306970835</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.07078415305225574</v>
+        <v>0.07064808818792088</v>
       </c>
       <c r="C93">
-        <v>404.0203827855576</v>
+        <v>386.6866224304651</v>
       </c>
       <c r="D93">
-        <v>2132.864082785557</v>
+        <v>2135.611022430465</v>
       </c>
       <c r="E93">
-        <v>1822.3737</v>
+        <v>1842.4544</v>
       </c>
       <c r="F93">
-        <v>1827.3437</v>
+        <v>1847.4244</v>
       </c>
       <c r="G93">
         <v>98.5</v>
@@ -8913,28 +8913,28 @@
         <v>401.1</v>
       </c>
       <c r="M93">
-        <v>112.01616881</v>
+        <v>113.24711572</v>
       </c>
       <c r="N93">
-        <v>289.08383119</v>
+        <v>287.85288428</v>
       </c>
       <c r="O93">
-        <v>85.27973020105</v>
+        <v>84.91660086259999</v>
       </c>
       <c r="P93">
-        <v>203.80410098895</v>
+        <v>202.9362834174</v>
       </c>
       <c r="Q93">
-        <v>206.20410098895</v>
+        <v>205.3362834174</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.3495237561361749</v>
+        <v>0.3861113523490112</v>
       </c>
       <c r="T93">
-        <v>4.69850991169712</v>
+        <v>5.264508388859732</v>
       </c>
       <c r="U93">
         <v>0.0613</v>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>3.58073306970835</v>
+        <v>3.541812058081085</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.07064808818792088</v>
+        <v>0.07051202332358604</v>
       </c>
       <c r="C94">
-        <v>386.6866224304651</v>
+        <v>369.3599468288437</v>
       </c>
       <c r="D94">
-        <v>2135.611022430465</v>
+        <v>2138.365046828844</v>
       </c>
       <c r="E94">
-        <v>1842.4544</v>
+        <v>1862.5351</v>
       </c>
       <c r="F94">
-        <v>1847.4244</v>
+        <v>1867.5051</v>
       </c>
       <c r="G94">
         <v>98.5</v>
@@ -8995,28 +8995,28 @@
         <v>401.1</v>
       </c>
       <c r="M94">
-        <v>113.24711572</v>
+        <v>114.47806263</v>
       </c>
       <c r="N94">
-        <v>287.85288428</v>
+        <v>286.62193737</v>
       </c>
       <c r="O94">
-        <v>84.91660086259999</v>
+        <v>84.55347152415</v>
       </c>
       <c r="P94">
-        <v>202.9362834174</v>
+        <v>202.06846584585</v>
       </c>
       <c r="Q94">
-        <v>205.3362834174</v>
+        <v>204.46846584585</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.3861113523490112</v>
+        <v>0.4331525474798009</v>
       </c>
       <c r="T94">
-        <v>5.264508388859732</v>
+        <v>5.992220716640235</v>
       </c>
       <c r="U94">
         <v>0.0613</v>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>3.541812058081085</v>
+        <v>3.503728057456557</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.07051202332358604</v>
+        <v>0.0722315184592512</v>
       </c>
       <c r="C95">
-        <v>369.3599468288437</v>
+        <v>314.9896873950599</v>
       </c>
       <c r="D95">
-        <v>2138.365046828844</v>
+        <v>2104.07548739506</v>
       </c>
       <c r="E95">
-        <v>1862.5351</v>
+        <v>1882.6158</v>
       </c>
       <c r="F95">
-        <v>1867.5051</v>
+        <v>1887.5858</v>
       </c>
       <c r="G95">
         <v>98.5</v>
@@ -9077,45 +9077,45 @@
         <v>401.1</v>
       </c>
       <c r="M95">
-        <v>114.47806263</v>
+        <v>120.99424978</v>
       </c>
       <c r="N95">
-        <v>286.62193737</v>
+        <v>280.10575022</v>
       </c>
       <c r="O95">
-        <v>84.55347152415</v>
+        <v>82.6311963149</v>
       </c>
       <c r="P95">
-        <v>202.06846584585</v>
+        <v>197.4745539051</v>
       </c>
       <c r="Q95">
-        <v>204.46846584585</v>
+        <v>199.8745539051</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.4331525474798009</v>
+        <v>0.4958741409875204</v>
       </c>
       <c r="T95">
-        <v>5.992220716640235</v>
+        <v>6.962503820347571</v>
       </c>
       <c r="U95">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V95">
         <v>0.295</v>
       </c>
       <c r="W95">
-        <v>0.0432165</v>
+        <v>0.04519050000000001</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y95">
-        <v>3.503728057456557</v>
+        <v>3.315033571672268</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.0722315184592512</v>
+        <v>0.07211519359491636</v>
       </c>
       <c r="C96">
-        <v>314.9896873950599</v>
+        <v>297.1939776841862</v>
       </c>
       <c r="D96">
-        <v>2104.07548739506</v>
+        <v>2106.360477684186</v>
       </c>
       <c r="E96">
-        <v>1882.6158</v>
+        <v>1902.6965</v>
       </c>
       <c r="F96">
-        <v>1887.5858</v>
+        <v>1907.6665</v>
       </c>
       <c r="G96">
         <v>98.5</v>
@@ -9159,28 +9159,28 @@
         <v>401.1</v>
       </c>
       <c r="M96">
-        <v>120.99424978</v>
+        <v>122.28142265</v>
       </c>
       <c r="N96">
-        <v>280.10575022</v>
+        <v>278.81857735</v>
       </c>
       <c r="O96">
-        <v>82.6311963149</v>
+        <v>82.25148031824999</v>
       </c>
       <c r="P96">
-        <v>197.4745539051</v>
+        <v>196.56709703175</v>
       </c>
       <c r="Q96">
-        <v>199.8745539051</v>
+        <v>198.96709703175</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.4958741409875204</v>
+        <v>0.5836843718983278</v>
       </c>
       <c r="T96">
-        <v>6.962503820347571</v>
+        <v>8.320900165537843</v>
       </c>
       <c r="U96">
         <v>0.0641</v>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>3.315033571672268</v>
+        <v>3.280138481444139</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.07211519359491636</v>
+        <v>0.07199886873058152</v>
       </c>
       <c r="C97">
-        <v>297.1939776841862</v>
+        <v>279.4032362902105</v>
       </c>
       <c r="D97">
-        <v>2106.360477684186</v>
+        <v>2108.650436290211</v>
       </c>
       <c r="E97">
-        <v>1902.6965</v>
+        <v>1922.7772</v>
       </c>
       <c r="F97">
-        <v>1907.6665</v>
+        <v>1927.7472</v>
       </c>
       <c r="G97">
         <v>98.5</v>
@@ -9241,28 +9241,28 @@
         <v>401.1</v>
       </c>
       <c r="M97">
-        <v>122.28142265</v>
+        <v>123.56859552</v>
       </c>
       <c r="N97">
-        <v>278.81857735</v>
+        <v>277.53140448</v>
       </c>
       <c r="O97">
-        <v>82.25148031824999</v>
+        <v>81.8717643216</v>
       </c>
       <c r="P97">
-        <v>196.56709703175</v>
+        <v>195.6596401584</v>
       </c>
       <c r="Q97">
-        <v>198.96709703175</v>
+        <v>198.0596401584</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.5836843718983278</v>
+        <v>0.715399718264539</v>
       </c>
       <c r="T97">
-        <v>8.320900165537843</v>
+        <v>10.35849468332325</v>
       </c>
       <c r="U97">
         <v>0.0641</v>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>3.280138481444139</v>
+        <v>3.24597037226243</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.07199886873058152</v>
+        <v>0.07188254386624668</v>
       </c>
       <c r="C98">
-        <v>279.4032362902108</v>
+        <v>261.6174794348899</v>
       </c>
       <c r="D98">
-        <v>2108.650436290211</v>
+        <v>2110.94537943489</v>
       </c>
       <c r="E98">
-        <v>1922.7772</v>
+        <v>1942.8579</v>
       </c>
       <c r="F98">
-        <v>1927.7472</v>
+        <v>1947.8279</v>
       </c>
       <c r="G98">
         <v>98.5</v>
@@ -9323,28 +9323,28 @@
         <v>401.1</v>
       </c>
       <c r="M98">
-        <v>123.56859552</v>
+        <v>124.85576839</v>
       </c>
       <c r="N98">
-        <v>277.53140448</v>
+        <v>276.24423161</v>
       </c>
       <c r="O98">
-        <v>81.87176432160001</v>
+        <v>81.49204832495001</v>
       </c>
       <c r="P98">
-        <v>195.6596401584</v>
+        <v>194.75218328505</v>
       </c>
       <c r="Q98">
-        <v>198.0596401584</v>
+        <v>197.15218328505</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.7153997182645372</v>
+        <v>0.9349252955415549</v>
       </c>
       <c r="T98">
-        <v>10.35849468332323</v>
+        <v>13.75448554629889</v>
       </c>
       <c r="U98">
         <v>0.0641</v>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>3.24597037226243</v>
+        <v>3.21250676017725</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.07188254386624668</v>
+        <v>0.07176621900191184</v>
       </c>
       <c r="C99">
-        <v>261.6174794348899</v>
+        <v>243.8367234106765</v>
       </c>
       <c r="D99">
-        <v>2110.94537943489</v>
+        <v>2113.245323410677</v>
       </c>
       <c r="E99">
-        <v>1942.8579</v>
+        <v>1962.9386</v>
       </c>
       <c r="F99">
-        <v>1947.8279</v>
+        <v>1967.9086</v>
       </c>
       <c r="G99">
         <v>98.5</v>
@@ -9405,28 +9405,28 @@
         <v>401.1</v>
       </c>
       <c r="M99">
-        <v>124.85576839</v>
+        <v>126.14294126</v>
       </c>
       <c r="N99">
-        <v>276.24423161</v>
+        <v>274.95705874</v>
       </c>
       <c r="O99">
-        <v>81.49204832495001</v>
+        <v>81.11233232830001</v>
       </c>
       <c r="P99">
-        <v>194.75218328505</v>
+        <v>193.8447264117</v>
       </c>
       <c r="Q99">
-        <v>197.15218328505</v>
+        <v>196.2447264117</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>0.9349252955415549</v>
+        <v>1.37397645009559</v>
       </c>
       <c r="T99">
-        <v>13.75448554629889</v>
+        <v>20.54646727225023</v>
       </c>
       <c r="U99">
         <v>0.0641</v>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>3.21250676017725</v>
+        <v>3.179726078950952</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.07176621900191184</v>
+        <v>0.07164989413757698</v>
       </c>
       <c r="C100">
-        <v>243.8367234106765</v>
+        <v>226.060984581107</v>
       </c>
       <c r="D100">
-        <v>2113.245323410677</v>
+        <v>2115.550284581107</v>
       </c>
       <c r="E100">
-        <v>1962.9386</v>
+        <v>1983.0193</v>
       </c>
       <c r="F100">
-        <v>1967.9086</v>
+        <v>1987.9893</v>
       </c>
       <c r="G100">
         <v>98.5</v>
@@ -9487,28 +9487,28 @@
         <v>401.1</v>
       </c>
       <c r="M100">
-        <v>126.14294126</v>
+        <v>127.43011413</v>
       </c>
       <c r="N100">
-        <v>274.95705874</v>
+        <v>273.66988587</v>
       </c>
       <c r="O100">
-        <v>81.11233232830001</v>
+        <v>80.73261633165001</v>
       </c>
       <c r="P100">
-        <v>193.8447264117</v>
+        <v>192.93726953835</v>
       </c>
       <c r="Q100">
-        <v>196.2447264117</v>
+        <v>195.33726953835</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.37397645009559</v>
+        <v>2.691129913757696</v>
       </c>
       <c r="T100">
-        <v>20.54646727225023</v>
+        <v>40.92241245010423</v>
       </c>
       <c r="U100">
         <v>0.0641</v>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>3.179726078950952</v>
+        <v>3.147607633709023</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.07164989413757698</v>
-      </c>
-      <c r="C101">
-        <v>226.060984581107</v>
-      </c>
-      <c r="D101">
-        <v>2115.550284581107</v>
-      </c>
-      <c r="E101">
-        <v>1983.0193</v>
-      </c>
-      <c r="F101">
-        <v>1987.9893</v>
-      </c>
-      <c r="G101">
-        <v>98.5</v>
-      </c>
-      <c r="H101">
-        <v>2003.1</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>403.5</v>
-      </c>
-      <c r="K101">
-        <v>2.4</v>
-      </c>
-      <c r="L101">
-        <v>401.1</v>
-      </c>
-      <c r="M101">
-        <v>127.43011413</v>
-      </c>
-      <c r="N101">
-        <v>273.66988587</v>
-      </c>
-      <c r="O101">
-        <v>80.73261633165001</v>
-      </c>
-      <c r="P101">
-        <v>192.93726953835</v>
-      </c>
-      <c r="Q101">
-        <v>195.33726953835</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>2.691129913757696</v>
-      </c>
-      <c r="T101">
-        <v>40.92241245010423</v>
-      </c>
-      <c r="U101">
-        <v>0.0641</v>
-      </c>
-      <c r="V101">
-        <v>0.295</v>
-      </c>
-      <c r="W101">
-        <v>0.04519050000000001</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>Ba2/BB</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>3.147607633709023</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
